--- a/vaud_apartments.xlsx
+++ b/vaud_apartments.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="All Listings" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="By Price per m2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Investment Ranking" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,8 +36,19 @@
       <b val="1"/>
       <color rgb="00006100"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -73,6 +85,36 @@
         <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+        <bgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000B050"/>
+        <bgColor rgb="0000B050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0092D050"/>
+        <bgColor rgb="0092D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF0000"/>
+        <bgColor rgb="00FF0000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -92,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -116,6 +158,84 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -481,17 +601,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC23"/>
+  <dimension ref="A1:AD25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="7" customWidth="1" min="11" max="11"/>
@@ -510,9 +630,10 @@
     <col width="30" customWidth="1" min="24" max="24"/>
     <col width="15" customWidth="1" min="25" max="25"/>
     <col width="30" customWidth="1" min="26" max="26"/>
-    <col width="22" customWidth="1" min="27" max="27"/>
-    <col width="21" customWidth="1" min="28" max="28"/>
-    <col width="18" customWidth="1" min="29" max="29"/>
+    <col width="30" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
+    <col width="21" customWidth="1" min="29" max="29"/>
+    <col width="18" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -648,15 +769,20 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>Image_Floor_Estimate</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Image_View_Estimate</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Image_Condition</t>
         </is>
@@ -665,10 +791,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rolle</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr"/>
+          <t>Nyon</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>1260</t>
+        </is>
+      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Apartment</t>
@@ -676,26 +806,24 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>780000</v>
+        <v>670000</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>17727</v>
+        <v>8272</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Rolle</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>2019</v>
-      </c>
+          <t>1260 Nyon,</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
@@ -712,7 +840,7 @@
       <c r="W2" s="2" t="inlineStr"/>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/cogestim-rolle-361/1559393/images/full/31642872.jpg; https://www.immobilier.ch/Medias/cogestim-rolle-361/1559393/images/full/31642858.jpg; https://www.immobilier.ch/Medias/cogestim-rolle-361/1559393/images/full/31642870.jpg; https://www.immobilier.ch/Medias/cogestim-rolle-361/1559393/images/full/31642861.jpg; https://www.immobilier.ch/Medias/cogestim-rolle-361/1559393/images/full/31642865.jpg</t>
+          <t>https://www.immobilier.ch/Medias/cologny-properties-3110/1593459/images/full/31960870.png; https://www.immobilier.ch/Medias/cologny-properties-3110/1593459/images/gridbig/31960870.png</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
@@ -722,24 +850,13 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/rolle/cogestim-rolle-361/charming-25-room-apartment-1559393</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>middle_floor</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>garden_view</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>well_lit</t>
-        </is>
-      </c>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/nyon/cologny-properties-3110/luxury-apartment-1593459</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AD2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -747,7 +864,11 @@
           <t>Gland</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>1196</t>
+        </is>
+      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Apartment</t>
@@ -759,21 +880,21 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>795000</v>
+        <v>550000</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>10890</v>
+        <v>6250</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Gland</t>
+          <t>1196 Gland,</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
@@ -783,7 +904,11 @@
       <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr"/>
       <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S3" s="2" t="inlineStr"/>
       <c r="T3" s="2" t="inlineStr"/>
       <c r="U3" s="2" t="inlineStr"/>
@@ -791,7 +916,7 @@
       <c r="W3" s="2" t="inlineStr"/>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/burnier-cie-sa-233/1576776/images/full/31805639.jpg; https://www.immobilier.ch/Medias/burnier-cie-sa-233/1576776/images/full/31805642.jpg; https://www.immobilier.ch/Medias/burnier-cie-sa-233/1576776/images/full/31805644.jpg; https://www.immobilier.ch/Medias/burnier-cie-sa-233/1576776/images/full/31805643.jpg; https://www.immobilier.ch/Medias/burnier-cie-sa-233/1576776/images/full/31805641.jpg</t>
+          <t>https://www.immobilier.ch/Medias/immo-vie-agee-sarl-2312/1591176/images/full/31940116.jpeg; https://www.immobilier.ch/Medias/immo-vie-agee-sarl-2312/1591176/images/full/31940122.jpeg; https://www.immobilier.ch/Medias/immo-vie-agee-sarl-2312/1591176/images/full/31940118.jpeg; https://www.immobilier.ch/Medias/immo-vie-agee-sarl-2312/1591176/images/full/31940120.jpeg; https://www.immobilier.ch/Medias/immo-vie-agee-sarl-2312/1591176/images/full/31940123.jpeg</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
@@ -801,24 +926,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/gland/burnier-cie-233/35-room-apartment-in-gland-1576776</t>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/gland/immo-vie-agee-sarl-2312/through-apartment-with-balconies-in-life-annuity-in-gland-1591176</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>lower_floor</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>garden_view</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>well_lit</t>
-        </is>
-      </c>
+          <t>Life annuity - occupied until 76yo dies</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -826,7 +944,11 @@
           <t>Gland</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>1196</t>
+        </is>
+      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Apartment</t>
@@ -848,7 +970,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Gland</t>
+          <t>1196 Gland,</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
@@ -865,7 +987,11 @@
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Yes (from images)</t>
+        </is>
+      </c>
       <c r="R4" s="2" t="inlineStr"/>
       <c r="S4" s="2" t="inlineStr"/>
       <c r="T4" s="2" t="inlineStr"/>
@@ -874,7 +1000,7 @@
       <c r="W4" s="2" t="inlineStr"/>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/dezage-sarl-2077/1525027/images/full/31291466.jpeg; https://www.immobilier.ch/Medias/dezage-sarl-2077/1525027/images/full/31291472.jpeg; https://www.immobilier.ch/Medias/dezage-sarl-2077/1525027/images/full/31291469.jpeg; https://www.immobilier.ch/Medias/dezage-sarl-2077/1525027/images/full/31291465.jpeg; https://www.immobilier.ch/Medias/dezage-sarl-2077/1525027/images/full/31291481.jpeg</t>
+          <t>https://www.immobilier.ch/Medias/omnia-immobilier-rolle-445/1460475/images/full/30616800.jpg; https://www.immobilier.ch/Medias/omnia-immobilier-rolle-445/1460475/images/gridbig/30616796.jpg; https://www.immobilier.ch/Medias/omnia-immobilier-rolle-445/1460475/images/full/30616796.jpg; https://www.immobilier.ch/Medias/omnia-immobilier-rolle-445/1460475/images/full/30616797.jpg; https://www.immobilier.ch/Medias/omnia-immobilier-rolle-445/1460475/images/full/30616799.jpg</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
@@ -884,13 +1010,18 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/gland/dezage-sarl-2077/charming-apartment-close-to-all-amenities-1525027</t>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/gland/omnia-immobilier-rolle-445/beautiful-35-room-apartment-in-gland-1460475</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr"/>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
+          <t>open_view</t>
+        </is>
+      </c>
+      <c r="AD4" s="2" t="inlineStr">
+        <is>
           <t>well_lit</t>
         </is>
       </c>
@@ -901,7 +1032,11 @@
           <t>Gland</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>1196</t>
+        </is>
+      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Apartment</t>
@@ -913,28 +1048,24 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>780000</v>
+        <v>795000</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>9512</v>
+        <v>10890</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Gland</t>
+          <t>1196 Gland,</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2008</v>
+        <v>1986</v>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr"/>
@@ -953,7 +1084,7 @@
       <c r="W5" s="2" t="inlineStr"/>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/omnia-immobilier-rolle-445/1460475/images/full/30616802.jpg; https://www.immobilier.ch/Medias/omnia-immobilier-rolle-445/1460475/images/full/30616798.jpg; https://www.immobilier.ch/Medias/omnia-immobilier-rolle-445/1460475/images/full/30616800.jpg; https://www.immobilier.ch/Medias/omnia-immobilier-rolle-445/1460475/images/full/30616801.jpg; https://www.immobilier.ch/Medias/omnia-immobilier-rolle-445/1460475/images/full/30616796.jpg</t>
+          <t>https://www.immobilier.ch/Medias/burnier-cie-sa-233/1576776/images/full/31805639.jpg; https://www.immobilier.ch/Medias/burnier-cie-sa-233/1576776/images/gridbig/31805643.jpg; https://www.immobilier.ch/Medias/burnier-cie-sa-233/1576776/images/full/31805640.jpg; https://www.immobilier.ch/Medias/burnier-cie-sa-233/1576776/images/full/31805645.jpg; https://www.immobilier.ch/Medias/burnier-cie-sa-233/1576776/images/full/31805644.jpg</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
@@ -963,16 +1094,21 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/gland/omnia-immobilier-rolle-445/beautiful-35-room-apartment-in-gland-1460475</t>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/gland/burnier-cie-233/35-room-apartment-in-gland-1576776</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr"/>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>open_view</t>
+          <t>middle_floor</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>garden_view</t>
+        </is>
+      </c>
+      <c r="AD5" s="2" t="inlineStr">
         <is>
           <t>well_lit</t>
         </is>
@@ -984,7 +1120,11 @@
           <t>Gland</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>1196</t>
+        </is>
+      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Apartment</t>
@@ -992,32 +1132,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>620000</v>
+        <v>780000</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>8611</v>
+        <v>9512</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Gland</t>
+          <t>1196 Gland,</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1988</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
+        <v>2008</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
@@ -1036,7 +1176,7 @@
       <c r="W6" s="2" t="inlineStr"/>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/roland-savary-immobilier-624/1574473/images/full/31783709.jpeg; https://www.immobilier.ch/Medias/roland-savary-immobilier-624/1574473/images/full/31783707.jpeg; https://www.immobilier.ch/Medias/roland-savary-immobilier-624/1574473/images/full/31783708.jpeg; https://www.immobilier.ch/Medias/roland-savary-immobilier-624/1574473/images/full/31783710.jpeg; https://www.immobilier.ch/Medias/roland-savary-immobilier-624/1574473/images/full/31783706.jpeg</t>
+          <t>https://www.immobilier.ch/Medias/dezage-sarl-2077/1581074/images/full/31844741.jpeg; https://www.immobilier.ch/Medias/dezage-sarl-2077/1581074/images/full/31844750.png; https://www.immobilier.ch/Medias/dezage-sarl-2077/1581074/images/full/31844740.jpeg; https://www.immobilier.ch/Medias/dezage-sarl-2077/1581074/images/full/31844748.jpeg; https://www.immobilier.ch/Medias/dezage-sarl-2077/1581074/images/full/31844744.jpeg</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
@@ -1046,20 +1186,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/gland/roland-savary-immobilier-624/gland-25-room-apartment-with-balcony-and-2-parking-spaces-included-in-the-price-1574473</t>
-        </is>
-      </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>middle_floor</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>garden_view</t>
-        </is>
-      </c>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/gland/dezage-sarl-2077/charming-apartment-close-to-all-amenities-1581074</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>open_view</t>
+        </is>
+      </c>
+      <c r="AD6" s="2" t="inlineStr">
         <is>
           <t>well_lit</t>
         </is>
@@ -1068,32 +1205,36 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Lausanne</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr"/>
+          <t>Gland</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>1196</t>
+        </is>
+      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Terrace flat</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>490000</v>
+        <v>720000</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>18846</v>
+        <v>9000</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Lausanne</t>
+          <t>1196 Gland,</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -1105,11 +1246,7 @@
       <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr"/>
       <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="R7" s="2" t="inlineStr"/>
       <c r="S7" s="2" t="inlineStr"/>
       <c r="T7" s="2" t="inlineStr"/>
       <c r="U7" s="2" t="inlineStr"/>
@@ -1117,7 +1254,7 @@
       <c r="W7" s="2" t="inlineStr"/>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/immo-v-3083/1574816/images/full/31787034.jpeg; https://www.immobilier.ch/Medias/immo-v-3083/1574816/images/full/31787030.jpeg; https://www.immobilier.ch/Medias/immo-v-3083/1574816/images/full/31787037.jpeg; https://www.immobilier.ch/Medias/immo-v-3083/1574816/images/full/31787040.jpeg; https://www.immobilier.ch/Medias/immo-v-3083/1574816/images/gridbig/31787042.png</t>
+          <t>https://www.immobilier.ch/Medias/i-particuliers-by-champeret-finances-1611/1584268/images/full/31876029.jpg; https://www.immobilier.ch/Medias/i-particuliers-by-champeret-finances-1611/1584268/images/full/31876026.jpg; https://www.immobilier.ch/Medias/i-particuliers-by-champeret-finances-1611/1584268/images/full/31876027.jpg; https://www.immobilier.ch/Medias/i-particuliers-by-champeret-finances-1611/1584268/images/full/31876024.jpg; https://www.immobilier.ch/Medias/i-particuliers-by-champeret-finances-1611/1584268/images/full/31876033.png</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
@@ -1127,12 +1264,25 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/immo-v-3083/renovated-and-furnished-with-terrace-ideal-location-1574816</t>
-        </is>
-      </c>
-      <c r="AA7" s="2" t="inlineStr"/>
-      <c r="AB7" s="2" t="inlineStr"/>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/gland/ikami-1611/magnificent-35-room-apartment-for-sale-gland-sold-with-tenant-078-403-10-20-1584268</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>Rented - tenant in place</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>middle_floor</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>garden_view</t>
+        </is>
+      </c>
+      <c r="AD7" s="2" t="inlineStr">
         <is>
           <t>well_lit</t>
         </is>
@@ -1144,7 +1294,11 @@
           <t>Lausanne</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>1012</t>
+        </is>
+      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Apartment</t>
@@ -1152,28 +1306,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>475000</v>
+        <v>560000</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>16379</v>
+        <v>12727</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Lausanne</t>
+          <t>1012 Lausanne,</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2026</v>
+        <v>1972</v>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
@@ -1188,7 +1346,7 @@
       <c r="W8" s="2" t="inlineStr"/>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/properti-ag-2229/1578008/images/full/31816414.jpeg; https://www.immobilier.ch/Medias/properti-ag-2229/1578008/images/full/31816421.jpg; https://www.immobilier.ch/Medias/properti-ag-2229/1578008/images/full/31816413.jpeg; https://www.immobilier.ch/Medias/properti-ag-2229/1578008/images/full/31816418.png; https://www.immobilier.ch/Medias/properti-ag-2229/1578008/images/full/31816425.png</t>
+          <t>https://www.immobilier.ch/Medias/golay-immobilier-sa-260/1593194/images/full/31958334.jpg; https://www.immobilier.ch/Medias/golay-immobilier-sa-260/1593194/images/full/31958329.jpg; https://www.immobilier.ch/Medias/golay-immobilier-sa-260/1593194/images/full/31958330.jpg; https://www.immobilier.ch/Medias/golay-immobilier-sa-260/1593194/images/full/31958326.jpg; https://www.immobilier.ch/Medias/golay-immobilier-sa-260/1593194/images/full/31958331.jpg</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
@@ -1198,13 +1356,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/properti-ag-2229/contemporary-address-in-the-heart-of-lausanne-1578008</t>
-        </is>
-      </c>
-      <c r="AA8" s="2" t="inlineStr"/>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/golay-immobilier-260/rented-2-room-apartment-lausanne-bethusy-district-1593194</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>Rented - tenant in place</t>
+        </is>
+      </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
+          <t>garden_view</t>
+        </is>
+      </c>
+      <c r="AD8" s="2" t="inlineStr">
+        <is>
           <t>renovated_modern</t>
         </is>
       </c>
@@ -1215,7 +1382,11 @@
           <t>Lausanne</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Apartment</t>
@@ -1237,18 +1408,14 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Lausanne</t>
+          <t>1010 Lausanne,</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr"/>
@@ -1263,7 +1430,7 @@
       <c r="W9" s="2" t="inlineStr"/>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/properti-ag-2229/1578011/images/full/31816454.jpeg; https://www.immobilier.ch/Medias/properti-ag-2229/1578011/images/full/31816453.jpeg; https://www.immobilier.ch/Medias/properti-ag-2229/1578011/images/gridbig/31816451.png; https://www.immobilier.ch/Medias/properti-ag-2229/1578011/images/full/31816455.jpg; https://www.immobilier.ch/Medias/properti-ag-2229/1578011/images/full/31816456.png</t>
+          <t>https://www.immobilier.ch/Medias/cardis-lausanne-429/1594479/images/full/31969322.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1594479/images/full/31969331.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1594479/images/gridbig/31969331.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1594479/images/full/31969344.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1594479/images/full/31969340.png</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
@@ -1273,16 +1440,13 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/properti-ag-2229/contemporary-address-in-the-heart-of-lausanne-1578011</t>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/switzerland-sothebys-lausanne-429/elegant-25-room-apartment-with-balcony-unit-05-1594479</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr"/>
       <c r="AB9" s="2" t="inlineStr"/>
-      <c r="AC9" s="2" t="inlineStr">
-        <is>
-          <t>well_lit</t>
-        </is>
-      </c>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1290,7 +1454,11 @@
           <t>Lausanne</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Apartment</t>
@@ -1298,32 +1466,28 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>585000</v>
+        <v>735000</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>16250</v>
+        <v>15312</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Lausanne</t>
+          <t>1010 Lausanne,</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
@@ -1338,7 +1502,7 @@
       <c r="W10" s="2" t="inlineStr"/>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/properti-ag-2229/1578014/images/full/31816484.jpeg; https://www.immobilier.ch/Medias/properti-ag-2229/1578014/images/full/31816485.jpeg; https://www.immobilier.ch/Medias/properti-ag-2229/1578014/images/full/31816489.jpg; https://www.immobilier.ch/Medias/properti-ag-2229/1578014/images/full/31816493.png; https://www.immobilier.ch/Medias/properti-ag-2229/1578014/images/gridbig/31816482.png</t>
+          <t>https://www.immobilier.ch/Medias/cardis-lausanne-429/1594481/images/full/31969367.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1594481/images/full/31969362.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1594481/images/full/31969366.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1594481/images/full/31969365.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1594481/images/full/31969358.png</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
@@ -1348,16 +1512,13 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/properti-ag-2229/contemporary-address-in-the-heart-of-lausanne-1578014</t>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/switzerland-sothebys-lausanne-429/contemporary-25-room-apartment-with-balcony-lot-02-1594481</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr"/>
       <c r="AB10" s="2" t="inlineStr"/>
-      <c r="AC10" s="2" t="inlineStr">
-        <is>
-          <t>well_lit</t>
-        </is>
-      </c>
+      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AD10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1365,7 +1526,11 @@
           <t>Lausanne</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Apartment</t>
@@ -1373,28 +1538,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>735000</v>
+        <v>480000</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>15312</v>
+        <v>16552</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Lausanne</t>
+          <t>1010 Lausanne,</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr"/>
@@ -1409,7 +1578,7 @@
       <c r="W11" s="2" t="inlineStr"/>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/properti-ag-2229/1578009/images/full/31816432.png; https://www.immobilier.ch/Medias/properti-ag-2229/1578009/images/full/31816434.png; https://www.immobilier.ch/Medias/properti-ag-2229/1578009/images/full/31816427.png; https://www.immobilier.ch/Medias/properti-ag-2229/1578009/images/full/31816426.jpeg; https://www.immobilier.ch/Medias/properti-ag-2229/1578009/images/full/31816431.jpg</t>
+          <t>https://www.immobilier.ch/Medias/cardis-lausanne-429/1594482/images/full/31969369.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1594482/images/gridbig/31969369.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1594482/images/full/31969383.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1594482/images/full/31969374.jpg; https://www.immobilier.ch/Medias/cardis-lausanne-429/1594482/images/full/31969373.png</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -1419,12 +1588,13 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/properti-ag-2229/contemporary-address-in-the-heart-of-lausanne-1578009</t>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/switzerland-sothebys-lausanne-429/contemporary-bright-studio-apartment-in-lausanne-lot-07-1594482</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr"/>
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AD11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1432,7 +1602,11 @@
           <t>Lausanne</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Apartment</t>
@@ -1440,24 +1614,26 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>740000</v>
+        <v>735000</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>7400</v>
+        <v>15312</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Lausanne</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
+          <t>1010 Lausanne,</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>2026</v>
+      </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
@@ -1474,7 +1650,7 @@
       <c r="W12" s="2" t="inlineStr"/>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/proximmo-sarl-622/1424896/images/gridbig/31543820.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1424896/images/full/31543820.jpg</t>
+          <t>https://www.immobilier.ch/Medias/properti-ag-2229/1592615/images/full/31952904.png; https://www.immobilier.ch/Medias/properti-ag-2229/1592615/images/full/31952895.jpeg; https://www.immobilier.ch/Medias/properti-ag-2229/1592615/images/full/31952907.png; https://www.immobilier.ch/Medias/properti-ag-2229/1592615/images/full/31952914.png; https://www.immobilier.ch/Medias/properti-ag-2229/1592615/images/gridbig/31952894.png</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1484,22 +1660,15 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/proximmo-agence-immobiliere-sarl-622/nouveau-quartier-15-min-lausanne-1424896</t>
-        </is>
-      </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>lower_floor</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>garden_view</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr">
-        <is>
-          <t>needs_work</t>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/properti-ag-2229/contemporary-address-in-the-heart-of-lausanne-1592615</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AD12" s="2" t="inlineStr">
+        <is>
+          <t>well_lit</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1678,11 @@
           <t>Lausanne</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Apartment</t>
@@ -1517,26 +1690,24 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>530000</v>
+        <v>670000</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>13947</v>
+        <v>8272</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Lausanne</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>1953</v>
-      </c>
+          <t>1003 Lausanne,</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
@@ -1544,16 +1715,8 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr"/>
       <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>Yes (from images)</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
       <c r="S13" s="2" t="inlineStr"/>
       <c r="T13" s="2" t="inlineStr"/>
       <c r="U13" s="2" t="inlineStr"/>
@@ -1561,7 +1724,7 @@
       <c r="W13" s="2" t="inlineStr"/>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/rham-ventes-lausanne-1873/1505625/images/full/31643539.jpg; https://www.immobilier.ch/Medias/rham-ventes-lausanne-1873/1505625/images/full/31643537.jpg; https://www.immobilier.ch/Medias/rham-ventes-lausanne-1873/1505625/images/full/31643540.jpg; https://www.immobilier.ch/Medias/rham-ventes-lausanne-1873/1505625/images/full/31643538.jpg; https://www.immobilier.ch/Medias/rham-ventes-lausanne-1873/1505625/images/gridbig/31643539.jpg</t>
+          <t>https://www.immobilier.ch/Medias/cologny-properties-3110/1593712/images/full/31962898.png; https://www.immobilier.ch/Medias/cologny-properties-3110/1593712/images/gridbig/31962898.png</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
@@ -1571,24 +1734,13 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/rham-ventes-lausanne-1873/for-sale-condominium-apartment-1010-lausanne-ap0196-1505625</t>
-        </is>
-      </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>upper_floor</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>open_view</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr">
-        <is>
-          <t>renovated_modern</t>
-        </is>
-      </c>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/cologny-properties-3110/luxury-apartment-1593712</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AD13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1596,34 +1748,42 @@
           <t>Lausanne</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Studio</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr"/>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>490000</v>
+        <v>750000</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>18846</v>
+        <v>15625</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Lausanne</t>
+          <t>1010 Lausanne,</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1969</v>
+        <v>2026</v>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr"/>
@@ -1631,16 +1791,8 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>Yes (from images)</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
       <c r="S14" s="2" t="inlineStr"/>
       <c r="T14" s="2" t="inlineStr"/>
       <c r="U14" s="2" t="inlineStr"/>
@@ -1648,7 +1800,7 @@
       <c r="W14" s="2" t="inlineStr"/>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/brymmo-2481/1545951/images/gridbig/31522051.jpg; https://www.immobilier.ch/Medias/brymmo-2481/1545951/images/full/31522052.jpg; https://www.immobilier.ch/Medias/brymmo-2481/1545951/images/full/31522056.jpg; https://www.immobilier.ch/Medias/brymmo-2481/1545951/images/full/31522054.jpg; https://www.immobilier.ch/Medias/brymmo-2481/1545951/images/full/31522055.jpg</t>
+          <t>https://www.immobilier.ch/Medias/properti-ag-2229/1592619/images/full/31952955.png; https://www.immobilier.ch/Medias/properti-ag-2229/1592619/images/full/31952947.jpeg; https://www.immobilier.ch/Medias/properti-ag-2229/1592619/images/full/31952953.jpg; https://www.immobilier.ch/Medias/properti-ag-2229/1592619/images/full/31952954.jpeg; https://www.immobilier.ch/Medias/properti-ag-2229/1592619/images/full/31952956.png</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -1658,16 +1810,13 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/brymmo-2481/jewel-in-the-heart-of-lausanne-1545951</t>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/properti-ag-2229/contemporary-address-in-the-heart-of-lausanne-1592619</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr"/>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>garden_view</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr">
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AD14" s="2" t="inlineStr">
         <is>
           <t>well_lit</t>
         </is>
@@ -1679,7 +1828,11 @@
           <t>Lausanne</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Apartment</t>
@@ -1694,14 +1847,14 @@
         <v>75</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>755000</v>
+        <v>750000</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>10067</v>
+        <v>10000</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Lausanne</t>
+          <t>1010 Lausanne,</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
@@ -1723,7 +1876,7 @@
       <c r="W15" s="2" t="inlineStr"/>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/cardis-lausanne-429/1551036/images/full/31567147.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1551036/images/full/31567143.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1551036/images/full/31567145.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1551036/images/full/31567148.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1551036/images/full/31567144.png</t>
+          <t>https://www.immobilier.ch/Medias/rham-ventes-lausanne-1873/1455126/images/full/30562727.jpg; https://www.immobilier.ch/Medias/rham-ventes-lausanne-1873/1455126/images/full/30562731.jpg; https://www.immobilier.ch/Medias/rham-ventes-lausanne-1873/1455126/images/gridbig/30562731.jpg; https://www.immobilier.ch/Medias/rham-ventes-lausanne-1873/1455126/images/full/30562728.jpg; https://www.immobilier.ch/Medias/rham-ventes-lausanne-1873/1455126/images/full/30562730.jpg</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
@@ -1733,12 +1886,17 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/switzerland-sothebys-lausanne-429/bright-apartment-with-wonderful-potential-1551036</t>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/rham-ventes-lausanne-1873/for-sale-condominium-apartment-1010-lausanne-ap0192-1455126</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr"/>
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AD15" s="2" t="inlineStr">
+        <is>
+          <t>needs_work</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1746,29 +1904,25 @@
           <t>Lausanne</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>75</v>
-      </c>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="3" t="n">
-        <v>750000</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>10000</v>
-      </c>
+        <v>250000</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Lausanne</t>
+          <t>1003 Lausanne,</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1788,7 +1942,7 @@
       <c r="W16" s="2" t="inlineStr"/>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/immo-ramma-2088/1476773/images/full/30788994.png; https://www.immobilier.ch/Medias/immo-ramma-2088/1476773/images/gridbig/30788994.png</t>
+          <t>https://www.immobilier.ch/Medias/proximmo-sarl-622/1484766/images/full/30935967.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1484766/images/gridbig/30935967.jpg</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -1798,12 +1952,21 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/immo-rama-2088/apartment-for-sale-in-lausanne-1476773</t>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/proximmo-agence-immobiliere-sarl-622/opportunities-for-private-investors-1484766</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr"/>
-      <c r="AB16" s="2" t="inlineStr"/>
-      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>lower_floor</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>garden_view</t>
+        </is>
+      </c>
+      <c r="AD16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1811,7 +1974,11 @@
           <t>Lausanne</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Apartment</t>
@@ -1819,20 +1986,26 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr"/>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>43</v>
+      </c>
       <c r="F17" s="3" t="n">
-        <v>420000</v>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
+        <v>550000</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>12791</v>
+      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Lausanne</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
+          <t>1005 Lausanne,</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>1942</v>
+      </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
@@ -1840,16 +2013,8 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr"/>
       <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>Yes (from images)</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
       <c r="S17" s="2" t="inlineStr"/>
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr"/>
@@ -1857,7 +2022,7 @@
       <c r="W17" s="2" t="inlineStr"/>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/kempter-immobilier-sarl-961/1544237/images/full/31494701.png; https://www.immobilier.ch/Medias/kempter-immobilier-sarl-961/1544237/images/full/31494707.png; https://www.immobilier.ch/Medias/kempter-immobilier-sarl-961/1544237/images/full/31494700.jpg; https://www.immobilier.ch/Medias/kempter-immobilier-sarl-961/1544237/images/full/31494699.jpg; https://www.immobilier.ch/Medias/kempter-immobilier-sarl-961/1544237/images/gridbig/31494707.png</t>
+          <t>https://www.immobilier.ch/Medias/regie-duboux-riviera-2599/1479348/images/gridbig/30813804.jpg; https://www.immobilier.ch/Medias/regie-duboux-riviera-2599/1479348/images/full/30813804.jpg; https://www.immobilier.ch/Medias/regie-duboux-riviera-2599/1479348/images/full/30813798.jpg; https://www.immobilier.ch/Medias/regie-duboux-riviera-2599/1479348/images/full/30813807.jpg; https://www.immobilier.ch/Medias/regie-duboux-riviera-2599/1479348/images/full/30813814.jpg</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
@@ -1867,20 +2032,21 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/kempter-immobilier-sarl-961/completely-renovated-studio-in-the-heart-of-lausanne-1544237</t>
-        </is>
-      </c>
-      <c r="AA17" s="2" t="inlineStr">
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/regie-duboux-riviera-2599/25-room-apartment-lausanne-1479348</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>upper_floor</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
+      <c r="AC17" s="2" t="inlineStr">
         <is>
           <t>open_view</t>
         </is>
       </c>
-      <c r="AC17" s="2" t="inlineStr">
+      <c r="AD17" s="2" t="inlineStr">
         <is>
           <t>well_lit</t>
         </is>
@@ -1892,43 +2058,53 @@
           <t>Lausanne</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Terrace flat</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>720000</v>
+        <v>490000</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>11613</v>
+        <v>18846</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Lausanne</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>1993</v>
-      </c>
+          <t>1004 Lausanne,</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr"/>
       <c r="Q18" s="2" t="inlineStr"/>
-      <c r="R18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S18" s="2" t="inlineStr"/>
       <c r="T18" s="2" t="inlineStr"/>
       <c r="U18" s="2" t="inlineStr"/>
@@ -1936,7 +2112,7 @@
       <c r="W18" s="2" t="inlineStr"/>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/actuaire-immobilier-1306/1237548/images/full/30898876.jpeg; https://www.immobilier.ch/Medias/actuaire-immobilier-1306/1237548/images/full/30898875.jpg; https://www.immobilier.ch/Medias/actuaire-immobilier-1306/1237548/images/gridbig/30898878.jpg; https://www.immobilier.ch/Medias/actuaire-immobilier-1306/1237548/images/full/30898878.jpg; https://www.immobilier.ch/Medias/actuaire-immobilier-1306/1237548/images/full/30898877.jpg</t>
+          <t>https://www.immobilier.ch/Medias/immo-v-3083/1588642/images/full/31916408.jpeg; https://www.immobilier.ch/Medias/immo-v-3083/1588642/images/full/31916411.jpeg; https://www.immobilier.ch/Medias/immo-v-3083/1588642/images/full/31916407.jpeg; https://www.immobilier.ch/Medias/immo-v-3083/1588642/images/full/31916396.jpeg; https://www.immobilier.ch/Medias/immo-v-3083/1588642/images/full/31916415.png</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
@@ -1946,14 +2122,15 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/actuaire-immobilier-1306/garden-level-apartment-area-under-the-train-station-in-lausanne-1237548</t>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/immo-v-3083/renovated-and-furnished-with-terrace-ideal-location-1588642</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr"/>
       <c r="AB18" s="2" t="inlineStr"/>
-      <c r="AC18" s="2" t="inlineStr">
-        <is>
-          <t>renovated_modern</t>
+      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AD18" s="2" t="inlineStr">
+        <is>
+          <t>well_lit</t>
         </is>
       </c>
     </row>
@@ -1963,7 +2140,11 @@
           <t>Lausanne</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Apartment</t>
@@ -1971,35 +2152,41 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>750000</v>
+        <v>585000</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>10000</v>
+        <v>11939</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Lausanne</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>1973</v>
-      </c>
+          <t>1004 Lausanne,</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr"/>
       <c r="Q19" s="2" t="inlineStr"/>
-      <c r="R19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S19" s="2" t="inlineStr"/>
       <c r="T19" s="2" t="inlineStr"/>
       <c r="U19" s="2" t="inlineStr"/>
@@ -2007,7 +2194,7 @@
       <c r="W19" s="2" t="inlineStr"/>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/rham-ventes-lausanne-1873/1455126/images/full/30562727.jpg; https://www.immobilier.ch/Medias/rham-ventes-lausanne-1873/1455126/images/full/30562728.jpg; https://www.immobilier.ch/Medias/rham-ventes-lausanne-1873/1455126/images/gridbig/30562731.jpg; https://www.immobilier.ch/Medias/rham-ventes-lausanne-1873/1455126/images/full/30562730.jpg; https://www.immobilier.ch/Medias/rham-ventes-lausanne-1873/1455126/images/full/30562729.jpg</t>
+          <t>https://www.immobilier.ch/Medias/proximmo-sarl-622/1581149/images/full/31845509.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1581149/images/full/31845508.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1581149/images/full/31845501.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1581149/images/full/31845502.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1581149/images/full/31845506.jpg</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2017,14 +2204,23 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/rham-ventes-lausanne-1873/for-sale-condominium-apartment-1010-lausanne-ap0192-1455126</t>
-        </is>
-      </c>
-      <c r="AA19" s="2" t="inlineStr"/>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/proximmo-agence-immobiliere-sarl-622/emplacement-rare-deux-pas-centre-ville-1581149</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>Rented - tenant in place</t>
+        </is>
+      </c>
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>well_lit</t>
+          <t>garden_view</t>
+        </is>
+      </c>
+      <c r="AD19" s="2" t="inlineStr">
+        <is>
+          <t>needs_work</t>
         </is>
       </c>
     </row>
@@ -2034,24 +2230,38 @@
           <t>Lausanne</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>75</v>
+      </c>
       <c r="F20" s="3" t="n">
-        <v>250000</v>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
+        <v>755000</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>10067</v>
+      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Lausanne</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
+          <t>1010 Lausanne,</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>1973</v>
+      </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
@@ -2068,7 +2278,7 @@
       <c r="W20" s="2" t="inlineStr"/>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/proximmo-sarl-622/1484766/images/full/30935967.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1484766/images/gridbig/30935967.jpg</t>
+          <t>https://www.immobilier.ch/Medias/cardis-lausanne-429/1551036/images/full/31567147.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1551036/images/full/31567148.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1551036/images/full/31567145.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1551036/images/full/31567143.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1551036/images/full/31567146.png</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
@@ -2078,20 +2288,13 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/proximmo-agence-immobiliere-sarl-622/opportunities-for-private-investors-1484766</t>
-        </is>
-      </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>lower_floor</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>garden_view</t>
-        </is>
-      </c>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/switzerland-sothebys-lausanne-429/bright-apartment-with-wonderful-potential-1551036</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AD20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2099,7 +2302,11 @@
           <t>Lausanne</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Apartment</t>
@@ -2107,28 +2314,28 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>129</v>
+        <v>49</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>770000</v>
+        <v>550000</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>5969</v>
+        <v>11224</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Lausanne</t>
+          <t>1004 Lausanne,</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr"/>
@@ -2137,7 +2344,11 @@
       <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S21" s="2" t="inlineStr"/>
       <c r="T21" s="2" t="inlineStr"/>
       <c r="U21" s="2" t="inlineStr"/>
@@ -2145,7 +2356,7 @@
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/proximmo-sarl-622/1485790/images/gridbig/31186861.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1485790/images/full/30936617.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1485790/images/full/30936615.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1485790/images/full/30936618.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1485790/images/full/30936619.jpg</t>
+          <t>https://www.immobilier.ch/Medias/proximmo-sarl-622/1581148/images/full/31845507.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1581148/images/full/31845503.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1581148/images/full/31845504.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1581148/images/full/31845505.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1581148/images/full/31845500.jpg</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2155,24 +2366,33 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/proximmo-agence-immobiliere-sarl-622/pierre-soleil-votre-nouveau-havre-paix-1485790</t>
-        </is>
-      </c>
-      <c r="AA21" s="2" t="inlineStr"/>
-      <c r="AB21" s="2" t="inlineStr">
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/proximmo-agence-immobiliere-sarl-622/emplacement-rare-deux-pas-centre-ville-1581148</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>Rented - tenant in place</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
         <is>
           <t>garden_view</t>
         </is>
       </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AD21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Morges</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr"/>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Apartment</t>
@@ -2180,30 +2400,28 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>760000</v>
+        <v>770000</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>8941</v>
+        <v>5969</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Morges</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>1985</v>
-      </c>
+          <t>1010 Lausanne,</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr"/>
@@ -2224,7 +2442,7 @@
       <c r="W22" s="2" t="inlineStr"/>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/vpi-courtage-467/1574988/images/full/31788726.jpg; https://www.immobilier.ch/Medias/vpi-courtage-467/1574988/images/gridbig/31788728.jpg; https://www.immobilier.ch/Medias/vpi-courtage-467/1574988/images/full/31788727.jpg; https://www.immobilier.ch/Medias/vpi-courtage-467/1574988/images/full/31788735.jpg; https://www.immobilier.ch/Medias/vpi-courtage-467/1574988/images/full/31788733.jpg</t>
+          <t>https://www.immobilier.ch/Medias/proximmo-sarl-622/1485790/images/full/30936618.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1485790/images/full/30936615.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1485790/images/full/30936619.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1485790/images/gridbig/31186861.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1485790/images/full/31186861.jpg</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -2234,18 +2452,19 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/morges/vpi-courtage-467/for-sale-apartment-1110-morges-6214567-1574988</t>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/proximmo-agence-immobiliere-sarl-622/votre-logement-familial-20-min-lausanne-1485790</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr"/>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>open_view</t>
-        </is>
-      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>renovated_modern</t>
+          <t>garden_view</t>
+        </is>
+      </c>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>well_lit</t>
         </is>
       </c>
     </row>
@@ -2255,7 +2474,11 @@
           <t>Morges</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>1110</t>
+        </is>
+      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Apartment</t>
@@ -2263,30 +2486,30 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>690000</v>
+        <v>730000</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>13800</v>
+        <v>6697</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Morges</t>
+          <t>1110 Morges,</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>2027</v>
+        <v>2013</v>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr"/>
@@ -2295,7 +2518,11 @@
       <c r="O23" s="2" t="inlineStr"/>
       <c r="P23" s="2" t="inlineStr"/>
       <c r="Q23" s="2" t="inlineStr"/>
-      <c r="R23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S23" s="2" t="inlineStr"/>
       <c r="T23" s="2" t="inlineStr"/>
       <c r="U23" s="2" t="inlineStr"/>
@@ -2303,7 +2530,7 @@
       <c r="W23" s="2" t="inlineStr"/>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/immocloud-sarl-2545/1564549/images/full/31718844.jpg; https://www.immobilier.ch/Medias/immocloud-sarl-2545/1564549/images/full/31718842.jpg; https://www.immobilier.ch/Medias/immocloud-sarl-2545/1564549/images/full/31718849.jpg; https://www.immobilier.ch/Medias/immocloud-sarl-2545/1564549/images/full/31718848.jpg; https://www.immobilier.ch/Medias/immocloud-sarl-2545/1564549/images/full/31692610.png</t>
+          <t>https://www.immobilier.ch/Medias/sev-immobilier-3069/1592927/images/full/31956104.jpg; https://www.immobilier.ch/Medias/sev-immobilier-3069/1592927/images/full/31956113.jpg; https://www.immobilier.ch/Medias/sev-immobilier-3069/1592927/images/gridbig/31956106.jpg; https://www.immobilier.ch/Medias/sev-immobilier-3069/1592927/images/full/31956101.jpg; https://www.immobilier.ch/Medias/sev-immobilier-3069/1592927/images/full/31956111.jpg</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
@@ -2313,18 +2540,183 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/morges/sev-immobilier-3069/for-sale-condominium-apartment-1110-morges-20261009-1592927</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>renovated_modern</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Morges</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>1110</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>690000</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>13800</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1110 Morges,</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>2027</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr"/>
+      <c r="W24" s="2" t="inlineStr"/>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/Medias/immocloud-sarl-2545/1564549/images/full/31692610.png; https://www.immobilier.ch/Medias/immocloud-sarl-2545/1564549/images/full/31718844.jpg; https://www.immobilier.ch/Medias/immocloud-sarl-2545/1564549/images/full/31718848.jpg; https://www.immobilier.ch/Medias/immocloud-sarl-2545/1564549/images/full/31718849.jpg; https://www.immobilier.ch/Medias/immocloud-sarl-2545/1564549/images/full/31718842.jpg</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>immobilier.ch</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
           <t>https://www.immobilier.ch/en/buy/apartment/vaud/morges/immocloud-sarl-2545/promotion-residence-cedre-the-construction-site-is-open-1564549</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr"/>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>garden_view</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr">
-        <is>
-          <t>needs_work</t>
+      <c r="AA24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>well_lit</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Morges</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>1110</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>760000</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>8941</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>1110 Morges,</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>1985</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr"/>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>Yes (from images)</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr"/>
+      <c r="W25" s="2" t="inlineStr"/>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/Medias/vpi-courtage-467/1587969/images/full/31910491.jpg; https://www.immobilier.ch/Medias/vpi-courtage-467/1587969/images/full/31910490.jpg; https://www.immobilier.ch/Medias/vpi-courtage-467/1587969/images/gridbig/31910490.jpg; https://www.immobilier.ch/Medias/vpi-courtage-467/1587969/images/full/31910494.jpg; https://www.immobilier.ch/Medias/vpi-courtage-467/1587969/images/full/31910493.jpg</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>immobilier.ch</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/morges/vpi-courtage-467/for-sale-apartment-1110-morges-6257755-1587969</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>open_view</t>
+        </is>
+      </c>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>renovated_modern</t>
         </is>
       </c>
     </row>
@@ -2339,182 +2731,194 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AE24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="7" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
     <col width="19" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="11" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
     <col width="30" customWidth="1" min="25" max="25"/>
     <col width="15" customWidth="1" min="26" max="26"/>
     <col width="30" customWidth="1" min="27" max="27"/>
-    <col width="21" customWidth="1" min="28" max="28"/>
-    <col width="17" customWidth="1" min="29" max="29"/>
+    <col width="30" customWidth="1" min="28" max="28"/>
+    <col width="22" customWidth="1" min="29" max="29"/>
+    <col width="21" customWidth="1" min="30" max="30"/>
+    <col width="18" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
           <t>City</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>NPA</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Property Type</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Rooms</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Size (m2)</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>Price (CHF)</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>Price/m2 (CHF)</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>Year Built</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>Parking</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>Floor</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>Cave/Cellar</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>Balcony</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>Terrace</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>Elevator</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>Renovated</t>
         </is>
       </c>
-      <c r="S1" s="4" t="inlineStr">
+      <c r="T1" s="4" t="inlineStr">
         <is>
           <t>New Construction</t>
         </is>
       </c>
-      <c r="T1" s="4" t="inlineStr">
+      <c r="U1" s="4" t="inlineStr">
         <is>
           <t>Energy Class</t>
         </is>
       </c>
-      <c r="U1" s="4" t="inlineStr">
+      <c r="V1" s="4" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="V1" s="4" t="inlineStr">
+      <c r="W1" s="4" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
       </c>
-      <c r="W1" s="4" t="inlineStr">
+      <c r="X1" s="4" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="X1" s="4" t="inlineStr">
+      <c r="Y1" s="4" t="inlineStr">
         <is>
           <t>Images</t>
         </is>
       </c>
-      <c r="Y1" s="4" t="inlineStr">
+      <c r="Z1" s="4" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="Z1" s="4" t="inlineStr">
+      <c r="AA1" s="4" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="AA1" s="4" t="inlineStr">
+      <c r="AB1" s="4" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="AC1" s="4" t="inlineStr">
         <is>
           <t>Image_Floor_Estimate</t>
         </is>
       </c>
-      <c r="AB1" s="4" t="inlineStr">
+      <c r="AD1" s="4" t="inlineStr">
         <is>
           <t>Image_View_Estimate</t>
         </is>
       </c>
-      <c r="AC1" s="4" t="inlineStr">
+      <c r="AE1" s="4" t="inlineStr">
         <is>
           <t>Image_Condition</t>
         </is>
@@ -2529,7 +2933,11 @@
           <t>Lausanne</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr"/>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
           <t>Apartment</t>
@@ -2537,7 +2945,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
@@ -2551,7 +2959,7 @@
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>Lausanne</t>
+          <t>1010 Lausanne,</t>
         </is>
       </c>
       <c r="J2" s="6" t="inlineStr"/>
@@ -2566,7 +2974,11 @@
       <c r="O2" s="6" t="inlineStr"/>
       <c r="P2" s="6" t="inlineStr"/>
       <c r="Q2" s="6" t="inlineStr"/>
-      <c r="R2" s="6" t="inlineStr"/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>Yes (from images)</t>
+        </is>
+      </c>
       <c r="S2" s="6" t="inlineStr"/>
       <c r="T2" s="6" t="inlineStr"/>
       <c r="U2" s="6" t="inlineStr"/>
@@ -2575,7 +2987,7 @@
       <c r="X2" s="6" t="inlineStr"/>
       <c r="Y2" s="6" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/proximmo-sarl-622/1485790/images/gridbig/31186861.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1485790/images/full/30936617.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1485790/images/full/30936615.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1485790/images/full/30936618.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1485790/images/full/30936619.jpg</t>
+          <t>https://www.immobilier.ch/Medias/proximmo-sarl-622/1485790/images/full/30936618.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1485790/images/full/30936615.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1485790/images/full/30936619.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1485790/images/gridbig/31186861.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1485790/images/full/31186861.jpg</t>
         </is>
       </c>
       <c r="Z2" s="6" t="inlineStr">
@@ -2585,16 +2997,21 @@
       </c>
       <c r="AA2" s="6" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/proximmo-agence-immobiliere-sarl-622/pierre-soleil-votre-nouveau-havre-paix-1485790</t>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/proximmo-agence-immobiliere-sarl-622/votre-logement-familial-20-min-lausanne-1485790</t>
         </is>
       </c>
       <c r="AB2" s="6" t="inlineStr"/>
-      <c r="AC2" s="6" t="inlineStr">
+      <c r="AC2" s="6" t="inlineStr"/>
+      <c r="AD2" s="6" t="inlineStr">
         <is>
           <t>garden_view</t>
         </is>
       </c>
-      <c r="AD2" s="2" t="inlineStr"/>
+      <c r="AE2" s="6" t="inlineStr">
+        <is>
+          <t>well_lit</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -2602,10 +3019,14 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Lausanne</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr"/>
+          <t>Gland</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>1196</t>
+        </is>
+      </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
           <t>Apartment</t>
@@ -2613,24 +3034,26 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>740000</v>
+        <v>550000</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>7400</v>
+        <v>6250</v>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>Lausanne</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr"/>
+          <t>1196 Gland,</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="n">
+        <v>1987</v>
+      </c>
       <c r="K3" s="6" t="inlineStr"/>
       <c r="L3" s="6" t="inlineStr"/>
       <c r="M3" s="6" t="inlineStr"/>
@@ -2639,7 +3062,11 @@
       <c r="P3" s="6" t="inlineStr"/>
       <c r="Q3" s="6" t="inlineStr"/>
       <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="T3" s="6" t="inlineStr"/>
       <c r="U3" s="6" t="inlineStr"/>
       <c r="V3" s="6" t="inlineStr"/>
@@ -2647,7 +3074,7 @@
       <c r="X3" s="6" t="inlineStr"/>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/proximmo-sarl-622/1424896/images/gridbig/31543820.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1424896/images/full/31543820.jpg</t>
+          <t>https://www.immobilier.ch/Medias/immo-vie-agee-sarl-2312/1591176/images/full/31940116.jpeg; https://www.immobilier.ch/Medias/immo-vie-agee-sarl-2312/1591176/images/full/31940122.jpeg; https://www.immobilier.ch/Medias/immo-vie-agee-sarl-2312/1591176/images/full/31940118.jpeg; https://www.immobilier.ch/Medias/immo-vie-agee-sarl-2312/1591176/images/full/31940120.jpeg; https://www.immobilier.ch/Medias/immo-vie-agee-sarl-2312/1591176/images/full/31940123.jpeg</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -2657,24 +3084,17 @@
       </c>
       <c r="AA3" s="6" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/proximmo-agence-immobiliere-sarl-622/nouveau-quartier-15-min-lausanne-1424896</t>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/gland/immo-vie-agee-sarl-2312/through-apartment-with-balconies-in-life-annuity-in-gland-1591176</t>
         </is>
       </c>
       <c r="AB3" s="6" t="inlineStr">
         <is>
-          <t>lower_floor</t>
-        </is>
-      </c>
-      <c r="AC3" s="6" t="inlineStr">
-        <is>
-          <t>garden_view</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>needs_work</t>
-        </is>
-      </c>
+          <t>Life annuity - occupied until 76yo dies</t>
+        </is>
+      </c>
+      <c r="AC3" s="6" t="inlineStr"/>
+      <c r="AD3" s="6" t="inlineStr"/>
+      <c r="AE3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
@@ -2682,10 +3102,14 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Gland</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr"/>
+          <t>Morges</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>1110</t>
+        </is>
+      </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Apartment</t>
@@ -2693,43 +3117,43 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>620000</v>
+        <v>730000</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>8611</v>
+        <v>6697</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>Gland</t>
+          <t>1110 Morges,</t>
         </is>
       </c>
       <c r="J4" s="6" t="n">
-        <v>1988</v>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
+        <v>2013</v>
+      </c>
+      <c r="K4" s="6" t="inlineStr"/>
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr"/>
       <c r="M4" s="6" t="inlineStr"/>
       <c r="N4" s="6" t="inlineStr"/>
       <c r="O4" s="6" t="inlineStr"/>
       <c r="P4" s="6" t="inlineStr"/>
       <c r="Q4" s="6" t="inlineStr"/>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>Yes (from images)</t>
-        </is>
-      </c>
-      <c r="S4" s="6" t="inlineStr"/>
+      <c r="R4" s="6" t="inlineStr"/>
+      <c r="S4" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="T4" s="6" t="inlineStr"/>
       <c r="U4" s="6" t="inlineStr"/>
       <c r="V4" s="6" t="inlineStr"/>
@@ -2737,7 +3161,7 @@
       <c r="X4" s="6" t="inlineStr"/>
       <c r="Y4" s="6" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/roland-savary-immobilier-624/1574473/images/full/31783709.jpeg; https://www.immobilier.ch/Medias/roland-savary-immobilier-624/1574473/images/full/31783707.jpeg; https://www.immobilier.ch/Medias/roland-savary-immobilier-624/1574473/images/full/31783708.jpeg; https://www.immobilier.ch/Medias/roland-savary-immobilier-624/1574473/images/full/31783710.jpeg; https://www.immobilier.ch/Medias/roland-savary-immobilier-624/1574473/images/full/31783706.jpeg</t>
+          <t>https://www.immobilier.ch/Medias/sev-immobilier-3069/1592927/images/full/31956104.jpg; https://www.immobilier.ch/Medias/sev-immobilier-3069/1592927/images/full/31956113.jpg; https://www.immobilier.ch/Medias/sev-immobilier-3069/1592927/images/gridbig/31956106.jpg; https://www.immobilier.ch/Medias/sev-immobilier-3069/1592927/images/full/31956101.jpg; https://www.immobilier.ch/Medias/sev-immobilier-3069/1592927/images/full/31956111.jpg</t>
         </is>
       </c>
       <c r="Z4" s="6" t="inlineStr">
@@ -2747,22 +3171,15 @@
       </c>
       <c r="AA4" s="6" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/gland/roland-savary-immobilier-624/gland-25-room-apartment-with-balcony-and-2-parking-spaces-included-in-the-price-1574473</t>
-        </is>
-      </c>
-      <c r="AB4" s="6" t="inlineStr">
-        <is>
-          <t>middle_floor</t>
-        </is>
-      </c>
-      <c r="AC4" s="6" t="inlineStr">
-        <is>
-          <t>garden_view</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="inlineStr">
-        <is>
-          <t>well_lit</t>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/morges/sev-immobilier-3069/for-sale-condominium-apartment-1110-morges-20261009-1592927</t>
+        </is>
+      </c>
+      <c r="AB4" s="6" t="inlineStr"/>
+      <c r="AC4" s="6" t="inlineStr"/>
+      <c r="AD4" s="6" t="inlineStr"/>
+      <c r="AE4" s="6" t="inlineStr">
+        <is>
+          <t>renovated_modern</t>
         </is>
       </c>
     </row>
@@ -2772,10 +3189,14 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Morges</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr"/>
+          <t>Nyon</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>1260</t>
+        </is>
+      </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Apartment</t>
@@ -2783,42 +3204,32 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="F5" s="6" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>760000</v>
+        <v>670000</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>8941</v>
+        <v>8272</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>Morges</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="n">
-        <v>1985</v>
-      </c>
+          <t>1260 Nyon,</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr"/>
       <c r="K5" s="6" t="inlineStr"/>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="L5" s="6" t="inlineStr"/>
       <c r="M5" s="6" t="inlineStr"/>
       <c r="N5" s="6" t="inlineStr"/>
       <c r="O5" s="6" t="inlineStr"/>
       <c r="P5" s="6" t="inlineStr"/>
       <c r="Q5" s="6" t="inlineStr"/>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>Yes (from images)</t>
-        </is>
-      </c>
+      <c r="R5" s="6" t="inlineStr"/>
       <c r="S5" s="6" t="inlineStr"/>
       <c r="T5" s="6" t="inlineStr"/>
       <c r="U5" s="6" t="inlineStr"/>
@@ -2827,7 +3238,7 @@
       <c r="X5" s="6" t="inlineStr"/>
       <c r="Y5" s="6" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/vpi-courtage-467/1574988/images/full/31788726.jpg; https://www.immobilier.ch/Medias/vpi-courtage-467/1574988/images/gridbig/31788728.jpg; https://www.immobilier.ch/Medias/vpi-courtage-467/1574988/images/full/31788727.jpg; https://www.immobilier.ch/Medias/vpi-courtage-467/1574988/images/full/31788735.jpg; https://www.immobilier.ch/Medias/vpi-courtage-467/1574988/images/full/31788733.jpg</t>
+          <t>https://www.immobilier.ch/Medias/cologny-properties-3110/1593459/images/full/31960870.png; https://www.immobilier.ch/Medias/cologny-properties-3110/1593459/images/gridbig/31960870.png</t>
         </is>
       </c>
       <c r="Z5" s="6" t="inlineStr">
@@ -2837,20 +3248,13 @@
       </c>
       <c r="AA5" s="6" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/morges/vpi-courtage-467/for-sale-apartment-1110-morges-6214567-1574988</t>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/nyon/cologny-properties-3110/luxury-apartment-1593459</t>
         </is>
       </c>
       <c r="AB5" s="6" t="inlineStr"/>
-      <c r="AC5" s="6" t="inlineStr">
-        <is>
-          <t>open_view</t>
-        </is>
-      </c>
-      <c r="AD5" s="2" t="inlineStr">
-        <is>
-          <t>renovated_modern</t>
-        </is>
-      </c>
+      <c r="AC5" s="6" t="inlineStr"/>
+      <c r="AD5" s="6" t="inlineStr"/>
+      <c r="AE5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
@@ -2858,10 +3262,14 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Gland</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr"/>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Apartment</t>
@@ -2873,28 +3281,22 @@
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>780000</v>
+        <v>670000</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>9512</v>
+        <v>8272</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>Gland</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="n">
-        <v>2008</v>
-      </c>
+          <t>1003 Lausanne,</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
       <c r="K6" s="6" t="inlineStr"/>
-      <c r="L6" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="L6" s="6" t="inlineStr"/>
       <c r="M6" s="6" t="inlineStr"/>
       <c r="N6" s="6" t="inlineStr"/>
       <c r="O6" s="6" t="inlineStr"/>
@@ -2909,7 +3311,7 @@
       <c r="X6" s="6" t="inlineStr"/>
       <c r="Y6" s="6" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/dezage-sarl-2077/1525027/images/full/31291466.jpeg; https://www.immobilier.ch/Medias/dezage-sarl-2077/1525027/images/full/31291472.jpeg; https://www.immobilier.ch/Medias/dezage-sarl-2077/1525027/images/full/31291469.jpeg; https://www.immobilier.ch/Medias/dezage-sarl-2077/1525027/images/full/31291465.jpeg; https://www.immobilier.ch/Medias/dezage-sarl-2077/1525027/images/full/31291481.jpeg</t>
+          <t>https://www.immobilier.ch/Medias/cologny-properties-3110/1593712/images/full/31962898.png; https://www.immobilier.ch/Medias/cologny-properties-3110/1593712/images/gridbig/31962898.png</t>
         </is>
       </c>
       <c r="Z6" s="6" t="inlineStr">
@@ -2919,16 +3321,13 @@
       </c>
       <c r="AA6" s="6" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/gland/dezage-sarl-2077/charming-apartment-close-to-all-amenities-1525027</t>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/cologny-properties-3110/luxury-apartment-1593712</t>
         </is>
       </c>
       <c r="AB6" s="6" t="inlineStr"/>
       <c r="AC6" s="6" t="inlineStr"/>
-      <c r="AD6" s="2" t="inlineStr">
-        <is>
-          <t>well_lit</t>
-        </is>
-      </c>
+      <c r="AD6" s="6" t="inlineStr"/>
+      <c r="AE6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -2936,10 +3335,14 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Gland</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr"/>
+          <t>Morges</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>1110</t>
+        </is>
+      </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Apartment</t>
@@ -2947,30 +3350,30 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>780000</v>
+        <v>760000</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>9512</v>
+        <v>8941</v>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>Gland</t>
+          <t>1110 Morges,</t>
         </is>
       </c>
       <c r="J7" s="6" t="n">
-        <v>2008</v>
+        <v>1985</v>
       </c>
       <c r="K7" s="6" t="inlineStr"/>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr"/>
@@ -2991,7 +3394,7 @@
       <c r="X7" s="6" t="inlineStr"/>
       <c r="Y7" s="6" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/omnia-immobilier-rolle-445/1460475/images/full/30616802.jpg; https://www.immobilier.ch/Medias/omnia-immobilier-rolle-445/1460475/images/full/30616798.jpg; https://www.immobilier.ch/Medias/omnia-immobilier-rolle-445/1460475/images/full/30616800.jpg; https://www.immobilier.ch/Medias/omnia-immobilier-rolle-445/1460475/images/full/30616801.jpg; https://www.immobilier.ch/Medias/omnia-immobilier-rolle-445/1460475/images/full/30616796.jpg</t>
+          <t>https://www.immobilier.ch/Medias/vpi-courtage-467/1587969/images/full/31910491.jpg; https://www.immobilier.ch/Medias/vpi-courtage-467/1587969/images/full/31910490.jpg; https://www.immobilier.ch/Medias/vpi-courtage-467/1587969/images/gridbig/31910490.jpg; https://www.immobilier.ch/Medias/vpi-courtage-467/1587969/images/full/31910494.jpg; https://www.immobilier.ch/Medias/vpi-courtage-467/1587969/images/full/31910493.jpg</t>
         </is>
       </c>
       <c r="Z7" s="6" t="inlineStr">
@@ -3001,232 +3404,292 @@
       </c>
       <c r="AA7" s="6" t="inlineStr">
         <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/morges/vpi-courtage-467/for-sale-apartment-1110-morges-6257755-1587969</t>
+        </is>
+      </c>
+      <c r="AB7" s="6" t="inlineStr"/>
+      <c r="AC7" s="6" t="inlineStr"/>
+      <c r="AD7" s="6" t="inlineStr">
+        <is>
+          <t>open_view</t>
+        </is>
+      </c>
+      <c r="AE7" s="6" t="inlineStr">
+        <is>
+          <t>renovated_modern</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Gland</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>1196</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>720000</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>1196 Gland,</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr"/>
+      <c r="K8" s="6" t="inlineStr"/>
+      <c r="L8" s="6" t="inlineStr"/>
+      <c r="M8" s="6" t="inlineStr"/>
+      <c r="N8" s="6" t="inlineStr"/>
+      <c r="O8" s="6" t="inlineStr"/>
+      <c r="P8" s="6" t="inlineStr"/>
+      <c r="Q8" s="6" t="inlineStr"/>
+      <c r="R8" s="6" t="inlineStr"/>
+      <c r="S8" s="6" t="inlineStr"/>
+      <c r="T8" s="6" t="inlineStr"/>
+      <c r="U8" s="6" t="inlineStr"/>
+      <c r="V8" s="6" t="inlineStr"/>
+      <c r="W8" s="6" t="inlineStr"/>
+      <c r="X8" s="6" t="inlineStr"/>
+      <c r="Y8" s="6" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/Medias/i-particuliers-by-champeret-finances-1611/1584268/images/full/31876029.jpg; https://www.immobilier.ch/Medias/i-particuliers-by-champeret-finances-1611/1584268/images/full/31876026.jpg; https://www.immobilier.ch/Medias/i-particuliers-by-champeret-finances-1611/1584268/images/full/31876027.jpg; https://www.immobilier.ch/Medias/i-particuliers-by-champeret-finances-1611/1584268/images/full/31876024.jpg; https://www.immobilier.ch/Medias/i-particuliers-by-champeret-finances-1611/1584268/images/full/31876033.png</t>
+        </is>
+      </c>
+      <c r="Z8" s="6" t="inlineStr">
+        <is>
+          <t>immobilier.ch</t>
+        </is>
+      </c>
+      <c r="AA8" s="6" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/gland/ikami-1611/magnificent-35-room-apartment-for-sale-gland-sold-with-tenant-078-403-10-20-1584268</t>
+        </is>
+      </c>
+      <c r="AB8" s="6" t="inlineStr">
+        <is>
+          <t>Rented - tenant in place</t>
+        </is>
+      </c>
+      <c r="AC8" s="6" t="inlineStr">
+        <is>
+          <t>middle_floor</t>
+        </is>
+      </c>
+      <c r="AD8" s="6" t="inlineStr">
+        <is>
+          <t>garden_view</t>
+        </is>
+      </c>
+      <c r="AE8" s="6" t="inlineStr">
+        <is>
+          <t>well_lit</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Gland</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>1196</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>780000</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>9512</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>1196 Gland,</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>2008</v>
+      </c>
+      <c r="K9" s="6" t="inlineStr"/>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr"/>
+      <c r="N9" s="6" t="inlineStr"/>
+      <c r="O9" s="6" t="inlineStr"/>
+      <c r="P9" s="6" t="inlineStr"/>
+      <c r="Q9" s="6" t="inlineStr"/>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>Yes (from images)</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr"/>
+      <c r="T9" s="6" t="inlineStr"/>
+      <c r="U9" s="6" t="inlineStr"/>
+      <c r="V9" s="6" t="inlineStr"/>
+      <c r="W9" s="6" t="inlineStr"/>
+      <c r="X9" s="6" t="inlineStr"/>
+      <c r="Y9" s="6" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/Medias/omnia-immobilier-rolle-445/1460475/images/full/30616800.jpg; https://www.immobilier.ch/Medias/omnia-immobilier-rolle-445/1460475/images/gridbig/30616796.jpg; https://www.immobilier.ch/Medias/omnia-immobilier-rolle-445/1460475/images/full/30616796.jpg; https://www.immobilier.ch/Medias/omnia-immobilier-rolle-445/1460475/images/full/30616797.jpg; https://www.immobilier.ch/Medias/omnia-immobilier-rolle-445/1460475/images/full/30616799.jpg</t>
+        </is>
+      </c>
+      <c r="Z9" s="6" t="inlineStr">
+        <is>
+          <t>immobilier.ch</t>
+        </is>
+      </c>
+      <c r="AA9" s="6" t="inlineStr">
+        <is>
           <t>https://www.immobilier.ch/en/buy/apartment/vaud/gland/omnia-immobilier-rolle-445/beautiful-35-room-apartment-in-gland-1460475</t>
         </is>
       </c>
-      <c r="AB7" s="6" t="inlineStr"/>
-      <c r="AC7" s="6" t="inlineStr">
+      <c r="AB9" s="6" t="inlineStr"/>
+      <c r="AC9" s="6" t="inlineStr"/>
+      <c r="AD9" s="6" t="inlineStr">
         <is>
           <t>open_view</t>
         </is>
       </c>
-      <c r="AD7" s="2" t="inlineStr">
+      <c r="AE9" s="6" t="inlineStr">
         <is>
           <t>well_lit</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Lausanne</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr"/>
-      <c r="D8" s="8" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Gland</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>1196</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
       </c>
-      <c r="F8" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>750000</v>
-      </c>
-      <c r="H8" s="9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>Lausanne</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr"/>
-      <c r="K8" s="8" t="inlineStr"/>
-      <c r="L8" s="8" t="inlineStr"/>
-      <c r="M8" s="8" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr"/>
-      <c r="O8" s="8" t="inlineStr"/>
-      <c r="P8" s="8" t="inlineStr"/>
-      <c r="Q8" s="8" t="inlineStr"/>
-      <c r="R8" s="8" t="inlineStr"/>
-      <c r="S8" s="8" t="inlineStr"/>
-      <c r="T8" s="8" t="inlineStr"/>
-      <c r="U8" s="8" t="inlineStr"/>
-      <c r="V8" s="8" t="inlineStr"/>
-      <c r="W8" s="8" t="inlineStr"/>
-      <c r="X8" s="8" t="inlineStr"/>
-      <c r="Y8" s="8" t="inlineStr">
-        <is>
-          <t>https://www.immobilier.ch/Medias/immo-ramma-2088/1476773/images/full/30788994.png; https://www.immobilier.ch/Medias/immo-ramma-2088/1476773/images/gridbig/30788994.png</t>
-        </is>
-      </c>
-      <c r="Z8" s="8" t="inlineStr">
+      <c r="F10" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>780000</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>9512</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>1196 Gland,</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>2008</v>
+      </c>
+      <c r="K10" s="6" t="inlineStr"/>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr"/>
+      <c r="N10" s="6" t="inlineStr"/>
+      <c r="O10" s="6" t="inlineStr"/>
+      <c r="P10" s="6" t="inlineStr"/>
+      <c r="Q10" s="6" t="inlineStr"/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>Yes (from images)</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr"/>
+      <c r="T10" s="6" t="inlineStr"/>
+      <c r="U10" s="6" t="inlineStr"/>
+      <c r="V10" s="6" t="inlineStr"/>
+      <c r="W10" s="6" t="inlineStr"/>
+      <c r="X10" s="6" t="inlineStr"/>
+      <c r="Y10" s="6" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/Medias/dezage-sarl-2077/1581074/images/full/31844741.jpeg; https://www.immobilier.ch/Medias/dezage-sarl-2077/1581074/images/full/31844750.png; https://www.immobilier.ch/Medias/dezage-sarl-2077/1581074/images/full/31844740.jpeg; https://www.immobilier.ch/Medias/dezage-sarl-2077/1581074/images/full/31844748.jpeg; https://www.immobilier.ch/Medias/dezage-sarl-2077/1581074/images/full/31844744.jpeg</t>
+        </is>
+      </c>
+      <c r="Z10" s="6" t="inlineStr">
         <is>
           <t>immobilier.ch</t>
         </is>
       </c>
-      <c r="AA8" s="8" t="inlineStr">
-        <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/immo-rama-2088/apartment-for-sale-in-lausanne-1476773</t>
-        </is>
-      </c>
-      <c r="AB8" s="8" t="inlineStr"/>
-      <c r="AC8" s="8" t="inlineStr"/>
-      <c r="AD8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Lausanne</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr"/>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Apartment</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="G9" s="9" t="n">
-        <v>750000</v>
-      </c>
-      <c r="H9" s="9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>Lausanne</t>
-        </is>
-      </c>
-      <c r="J9" s="8" t="n">
-        <v>1973</v>
-      </c>
-      <c r="K9" s="8" t="inlineStr"/>
-      <c r="L9" s="8" t="inlineStr"/>
-      <c r="M9" s="8" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr"/>
-      <c r="O9" s="8" t="inlineStr"/>
-      <c r="P9" s="8" t="inlineStr"/>
-      <c r="Q9" s="8" t="inlineStr"/>
-      <c r="R9" s="8" t="inlineStr"/>
-      <c r="S9" s="8" t="inlineStr"/>
-      <c r="T9" s="8" t="inlineStr"/>
-      <c r="U9" s="8" t="inlineStr"/>
-      <c r="V9" s="8" t="inlineStr"/>
-      <c r="W9" s="8" t="inlineStr"/>
-      <c r="X9" s="8" t="inlineStr"/>
-      <c r="Y9" s="8" t="inlineStr">
-        <is>
-          <t>https://www.immobilier.ch/Medias/rham-ventes-lausanne-1873/1455126/images/full/30562727.jpg; https://www.immobilier.ch/Medias/rham-ventes-lausanne-1873/1455126/images/full/30562728.jpg; https://www.immobilier.ch/Medias/rham-ventes-lausanne-1873/1455126/images/gridbig/30562731.jpg; https://www.immobilier.ch/Medias/rham-ventes-lausanne-1873/1455126/images/full/30562730.jpg; https://www.immobilier.ch/Medias/rham-ventes-lausanne-1873/1455126/images/full/30562729.jpg</t>
-        </is>
-      </c>
-      <c r="Z9" s="8" t="inlineStr">
-        <is>
-          <t>immobilier.ch</t>
-        </is>
-      </c>
-      <c r="AA9" s="8" t="inlineStr">
-        <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/rham-ventes-lausanne-1873/for-sale-condominium-apartment-1010-lausanne-ap0192-1455126</t>
-        </is>
-      </c>
-      <c r="AB9" s="8" t="inlineStr"/>
-      <c r="AC9" s="8" t="inlineStr"/>
-      <c r="AD9" s="2" t="inlineStr">
+      <c r="AA10" s="6" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/gland/dezage-sarl-2077/charming-apartment-close-to-all-amenities-1581074</t>
+        </is>
+      </c>
+      <c r="AB10" s="6" t="inlineStr"/>
+      <c r="AC10" s="6" t="inlineStr"/>
+      <c r="AD10" s="6" t="inlineStr">
+        <is>
+          <t>open_view</t>
+        </is>
+      </c>
+      <c r="AE10" s="6" t="inlineStr">
         <is>
           <t>well_lit</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Lausanne</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr"/>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Apartment</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="G10" s="9" t="n">
-        <v>755000</v>
-      </c>
-      <c r="H10" s="9" t="n">
-        <v>10067</v>
-      </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>Lausanne</t>
-        </is>
-      </c>
-      <c r="J10" s="8" t="n">
-        <v>1973</v>
-      </c>
-      <c r="K10" s="8" t="inlineStr"/>
-      <c r="L10" s="8" t="inlineStr"/>
-      <c r="M10" s="8" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr"/>
-      <c r="O10" s="8" t="inlineStr"/>
-      <c r="P10" s="8" t="inlineStr"/>
-      <c r="Q10" s="8" t="inlineStr"/>
-      <c r="R10" s="8" t="inlineStr"/>
-      <c r="S10" s="8" t="inlineStr"/>
-      <c r="T10" s="8" t="inlineStr"/>
-      <c r="U10" s="8" t="inlineStr"/>
-      <c r="V10" s="8" t="inlineStr"/>
-      <c r="W10" s="8" t="inlineStr"/>
-      <c r="X10" s="8" t="inlineStr"/>
-      <c r="Y10" s="8" t="inlineStr">
-        <is>
-          <t>https://www.immobilier.ch/Medias/cardis-lausanne-429/1551036/images/full/31567147.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1551036/images/full/31567143.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1551036/images/full/31567145.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1551036/images/full/31567148.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1551036/images/full/31567144.png</t>
-        </is>
-      </c>
-      <c r="Z10" s="8" t="inlineStr">
-        <is>
-          <t>immobilier.ch</t>
-        </is>
-      </c>
-      <c r="AA10" s="8" t="inlineStr">
-        <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/switzerland-sothebys-lausanne-429/bright-apartment-with-wonderful-potential-1551036</t>
-        </is>
-      </c>
-      <c r="AB10" s="8" t="inlineStr"/>
-      <c r="AC10" s="8" t="inlineStr"/>
-      <c r="AD10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -3234,10 +3697,14 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Gland</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr"/>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
           <t>Apartment</t>
@@ -3249,21 +3716,21 @@
         </is>
       </c>
       <c r="F11" s="8" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>795000</v>
+        <v>750000</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>10890</v>
+        <v>10000</v>
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>Gland</t>
+          <t>1010 Lausanne,</t>
         </is>
       </c>
       <c r="J11" s="8" t="n">
-        <v>1986</v>
+        <v>1973</v>
       </c>
       <c r="K11" s="8" t="inlineStr"/>
       <c r="L11" s="8" t="inlineStr"/>
@@ -3281,7 +3748,7 @@
       <c r="X11" s="8" t="inlineStr"/>
       <c r="Y11" s="8" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/burnier-cie-sa-233/1576776/images/full/31805639.jpg; https://www.immobilier.ch/Medias/burnier-cie-sa-233/1576776/images/full/31805642.jpg; https://www.immobilier.ch/Medias/burnier-cie-sa-233/1576776/images/full/31805644.jpg; https://www.immobilier.ch/Medias/burnier-cie-sa-233/1576776/images/full/31805643.jpg; https://www.immobilier.ch/Medias/burnier-cie-sa-233/1576776/images/full/31805641.jpg</t>
+          <t>https://www.immobilier.ch/Medias/rham-ventes-lausanne-1873/1455126/images/full/30562727.jpg; https://www.immobilier.ch/Medias/rham-ventes-lausanne-1873/1455126/images/full/30562731.jpg; https://www.immobilier.ch/Medias/rham-ventes-lausanne-1873/1455126/images/gridbig/30562731.jpg; https://www.immobilier.ch/Medias/rham-ventes-lausanne-1873/1455126/images/full/30562728.jpg; https://www.immobilier.ch/Medias/rham-ventes-lausanne-1873/1455126/images/full/30562730.jpg</t>
         </is>
       </c>
       <c r="Z11" s="8" t="inlineStr">
@@ -3291,22 +3758,15 @@
       </c>
       <c r="AA11" s="8" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/gland/burnier-cie-233/35-room-apartment-in-gland-1576776</t>
-        </is>
-      </c>
-      <c r="AB11" s="8" t="inlineStr">
-        <is>
-          <t>lower_floor</t>
-        </is>
-      </c>
-      <c r="AC11" s="8" t="inlineStr">
-        <is>
-          <t>garden_view</t>
-        </is>
-      </c>
-      <c r="AD11" s="2" t="inlineStr">
-        <is>
-          <t>well_lit</t>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/rham-ventes-lausanne-1873/for-sale-condominium-apartment-1010-lausanne-ap0192-1455126</t>
+        </is>
+      </c>
+      <c r="AB11" s="8" t="inlineStr"/>
+      <c r="AC11" s="8" t="inlineStr"/>
+      <c r="AD11" s="8" t="inlineStr"/>
+      <c r="AE11" s="8" t="inlineStr">
+        <is>
+          <t>needs_work</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3779,11 @@
           <t>Lausanne</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr"/>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
           <t>Apartment</t>
@@ -3327,25 +3791,25 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="F12" s="8" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>720000</v>
+        <v>755000</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>11613</v>
+        <v>10067</v>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>Lausanne</t>
+          <t>1010 Lausanne,</t>
         </is>
       </c>
       <c r="J12" s="8" t="n">
-        <v>1993</v>
+        <v>1973</v>
       </c>
       <c r="K12" s="8" t="inlineStr"/>
       <c r="L12" s="8" t="inlineStr"/>
@@ -3363,7 +3827,7 @@
       <c r="X12" s="8" t="inlineStr"/>
       <c r="Y12" s="8" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/actuaire-immobilier-1306/1237548/images/full/30898876.jpeg; https://www.immobilier.ch/Medias/actuaire-immobilier-1306/1237548/images/full/30898875.jpg; https://www.immobilier.ch/Medias/actuaire-immobilier-1306/1237548/images/gridbig/30898878.jpg; https://www.immobilier.ch/Medias/actuaire-immobilier-1306/1237548/images/full/30898878.jpg; https://www.immobilier.ch/Medias/actuaire-immobilier-1306/1237548/images/full/30898877.jpg</t>
+          <t>https://www.immobilier.ch/Medias/cardis-lausanne-429/1551036/images/full/31567147.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1551036/images/full/31567148.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1551036/images/full/31567145.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1551036/images/full/31567143.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1551036/images/full/31567146.png</t>
         </is>
       </c>
       <c r="Z12" s="8" t="inlineStr">
@@ -3373,16 +3837,13 @@
       </c>
       <c r="AA12" s="8" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/actuaire-immobilier-1306/garden-level-apartment-area-under-the-train-station-in-lausanne-1237548</t>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/switzerland-sothebys-lausanne-429/bright-apartment-with-wonderful-potential-1551036</t>
         </is>
       </c>
       <c r="AB12" s="8" t="inlineStr"/>
       <c r="AC12" s="8" t="inlineStr"/>
-      <c r="AD12" s="2" t="inlineStr">
-        <is>
-          <t>renovated_modern</t>
-        </is>
-      </c>
+      <c r="AD12" s="8" t="inlineStr"/>
+      <c r="AE12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -3390,10 +3851,14 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Morges</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr"/>
+          <t>Gland</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>1196</t>
+        </is>
+      </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
           <t>Apartment</t>
@@ -3401,38 +3866,38 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="F13" s="8" t="n">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>690000</v>
+        <v>795000</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>13800</v>
+        <v>10890</v>
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>Morges</t>
+          <t>1196 Gland,</t>
         </is>
       </c>
       <c r="J13" s="8" t="n">
-        <v>2027</v>
+        <v>1986</v>
       </c>
       <c r="K13" s="8" t="inlineStr"/>
-      <c r="L13" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="L13" s="8" t="inlineStr"/>
       <c r="M13" s="8" t="inlineStr"/>
       <c r="N13" s="8" t="inlineStr"/>
       <c r="O13" s="8" t="inlineStr"/>
       <c r="P13" s="8" t="inlineStr"/>
       <c r="Q13" s="8" t="inlineStr"/>
-      <c r="R13" s="8" t="inlineStr"/>
+      <c r="R13" s="8" t="inlineStr">
+        <is>
+          <t>Yes (from images)</t>
+        </is>
+      </c>
       <c r="S13" s="8" t="inlineStr"/>
       <c r="T13" s="8" t="inlineStr"/>
       <c r="U13" s="8" t="inlineStr"/>
@@ -3441,7 +3906,7 @@
       <c r="X13" s="8" t="inlineStr"/>
       <c r="Y13" s="8" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/immocloud-sarl-2545/1564549/images/full/31718844.jpg; https://www.immobilier.ch/Medias/immocloud-sarl-2545/1564549/images/full/31718842.jpg; https://www.immobilier.ch/Medias/immocloud-sarl-2545/1564549/images/full/31718849.jpg; https://www.immobilier.ch/Medias/immocloud-sarl-2545/1564549/images/full/31718848.jpg; https://www.immobilier.ch/Medias/immocloud-sarl-2545/1564549/images/full/31692610.png</t>
+          <t>https://www.immobilier.ch/Medias/burnier-cie-sa-233/1576776/images/full/31805639.jpg; https://www.immobilier.ch/Medias/burnier-cie-sa-233/1576776/images/gridbig/31805643.jpg; https://www.immobilier.ch/Medias/burnier-cie-sa-233/1576776/images/full/31805640.jpg; https://www.immobilier.ch/Medias/burnier-cie-sa-233/1576776/images/full/31805645.jpg; https://www.immobilier.ch/Medias/burnier-cie-sa-233/1576776/images/full/31805644.jpg</t>
         </is>
       </c>
       <c r="Z13" s="8" t="inlineStr">
@@ -3451,18 +3916,23 @@
       </c>
       <c r="AA13" s="8" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/morges/immocloud-sarl-2545/promotion-residence-cedre-the-construction-site-is-open-1564549</t>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/gland/burnier-cie-233/35-room-apartment-in-gland-1576776</t>
         </is>
       </c>
       <c r="AB13" s="8" t="inlineStr"/>
       <c r="AC13" s="8" t="inlineStr">
         <is>
+          <t>middle_floor</t>
+        </is>
+      </c>
+      <c r="AD13" s="8" t="inlineStr">
+        <is>
           <t>garden_view</t>
         </is>
       </c>
-      <c r="AD13" s="2" t="inlineStr">
-        <is>
-          <t>needs_work</t>
+      <c r="AE13" s="8" t="inlineStr">
+        <is>
+          <t>well_lit</t>
         </is>
       </c>
     </row>
@@ -3475,7 +3945,11 @@
           <t>Lausanne</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr"/>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Apartment</t>
@@ -3483,38 +3957,36 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="F14" s="8" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>530000</v>
+        <v>550000</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>13947</v>
+        <v>11224</v>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>Lausanne</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="n">
-        <v>1953</v>
-      </c>
+          <t>1004 Lausanne,</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr"/>
       <c r="K14" s="8" t="inlineStr"/>
-      <c r="L14" s="8" t="inlineStr"/>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="M14" s="8" t="inlineStr"/>
       <c r="N14" s="8" t="inlineStr"/>
       <c r="O14" s="8" t="inlineStr"/>
       <c r="P14" s="8" t="inlineStr"/>
       <c r="Q14" s="8" t="inlineStr"/>
-      <c r="R14" s="8" t="inlineStr">
-        <is>
-          <t>Yes (from images)</t>
-        </is>
-      </c>
+      <c r="R14" s="8" t="inlineStr"/>
       <c r="S14" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3527,7 +3999,7 @@
       <c r="X14" s="8" t="inlineStr"/>
       <c r="Y14" s="8" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/rham-ventes-lausanne-1873/1505625/images/full/31643539.jpg; https://www.immobilier.ch/Medias/rham-ventes-lausanne-1873/1505625/images/full/31643537.jpg; https://www.immobilier.ch/Medias/rham-ventes-lausanne-1873/1505625/images/full/31643540.jpg; https://www.immobilier.ch/Medias/rham-ventes-lausanne-1873/1505625/images/full/31643538.jpg; https://www.immobilier.ch/Medias/rham-ventes-lausanne-1873/1505625/images/gridbig/31643539.jpg</t>
+          <t>https://www.immobilier.ch/Medias/proximmo-sarl-622/1581148/images/full/31845507.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1581148/images/full/31845503.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1581148/images/full/31845504.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1581148/images/full/31845505.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1581148/images/full/31845500.jpg</t>
         </is>
       </c>
       <c r="Z14" s="8" t="inlineStr">
@@ -3537,322 +4009,373 @@
       </c>
       <c r="AA14" s="8" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/rham-ventes-lausanne-1873/for-sale-condominium-apartment-1010-lausanne-ap0196-1505625</t>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/proximmo-agence-immobiliere-sarl-622/emplacement-rare-deux-pas-centre-ville-1581148</t>
         </is>
       </c>
       <c r="AB14" s="8" t="inlineStr">
         <is>
+          <t>Rented - tenant in place</t>
+        </is>
+      </c>
+      <c r="AC14" s="8" t="inlineStr"/>
+      <c r="AD14" s="8" t="inlineStr">
+        <is>
+          <t>garden_view</t>
+        </is>
+      </c>
+      <c r="AE14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>585000</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>11939</v>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>1004 Lausanne,</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr"/>
+      <c r="K15" s="8" t="inlineStr"/>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="M15" s="8" t="inlineStr"/>
+      <c r="N15" s="8" t="inlineStr"/>
+      <c r="O15" s="8" t="inlineStr"/>
+      <c r="P15" s="8" t="inlineStr"/>
+      <c r="Q15" s="8" t="inlineStr"/>
+      <c r="R15" s="8" t="inlineStr"/>
+      <c r="S15" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr"/>
+      <c r="U15" s="8" t="inlineStr"/>
+      <c r="V15" s="8" t="inlineStr"/>
+      <c r="W15" s="8" t="inlineStr"/>
+      <c r="X15" s="8" t="inlineStr"/>
+      <c r="Y15" s="8" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/Medias/proximmo-sarl-622/1581149/images/full/31845509.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1581149/images/full/31845508.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1581149/images/full/31845501.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1581149/images/full/31845502.jpg; https://www.immobilier.ch/Medias/proximmo-sarl-622/1581149/images/full/31845506.jpg</t>
+        </is>
+      </c>
+      <c r="Z15" s="8" t="inlineStr">
+        <is>
+          <t>immobilier.ch</t>
+        </is>
+      </c>
+      <c r="AA15" s="8" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/proximmo-agence-immobiliere-sarl-622/emplacement-rare-deux-pas-centre-ville-1581149</t>
+        </is>
+      </c>
+      <c r="AB15" s="8" t="inlineStr">
+        <is>
+          <t>Rented - tenant in place</t>
+        </is>
+      </c>
+      <c r="AC15" s="8" t="inlineStr"/>
+      <c r="AD15" s="8" t="inlineStr">
+        <is>
+          <t>garden_view</t>
+        </is>
+      </c>
+      <c r="AE15" s="8" t="inlineStr">
+        <is>
+          <t>needs_work</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>1012</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>560000</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>12727</v>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>1012 Lausanne,</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="n">
+        <v>1972</v>
+      </c>
+      <c r="K16" s="8" t="inlineStr"/>
+      <c r="L16" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M16" s="8" t="inlineStr"/>
+      <c r="N16" s="8" t="inlineStr"/>
+      <c r="O16" s="8" t="inlineStr"/>
+      <c r="P16" s="8" t="inlineStr"/>
+      <c r="Q16" s="8" t="inlineStr"/>
+      <c r="R16" s="8" t="inlineStr"/>
+      <c r="S16" s="8" t="inlineStr"/>
+      <c r="T16" s="8" t="inlineStr"/>
+      <c r="U16" s="8" t="inlineStr"/>
+      <c r="V16" s="8" t="inlineStr"/>
+      <c r="W16" s="8" t="inlineStr"/>
+      <c r="X16" s="8" t="inlineStr"/>
+      <c r="Y16" s="8" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/Medias/golay-immobilier-sa-260/1593194/images/full/31958334.jpg; https://www.immobilier.ch/Medias/golay-immobilier-sa-260/1593194/images/full/31958329.jpg; https://www.immobilier.ch/Medias/golay-immobilier-sa-260/1593194/images/full/31958330.jpg; https://www.immobilier.ch/Medias/golay-immobilier-sa-260/1593194/images/full/31958326.jpg; https://www.immobilier.ch/Medias/golay-immobilier-sa-260/1593194/images/full/31958331.jpg</t>
+        </is>
+      </c>
+      <c r="Z16" s="8" t="inlineStr">
+        <is>
+          <t>immobilier.ch</t>
+        </is>
+      </c>
+      <c r="AA16" s="8" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/golay-immobilier-260/rented-2-room-apartment-lausanne-bethusy-district-1593194</t>
+        </is>
+      </c>
+      <c r="AB16" s="8" t="inlineStr">
+        <is>
+          <t>Rented - tenant in place</t>
+        </is>
+      </c>
+      <c r="AC16" s="8" t="inlineStr"/>
+      <c r="AD16" s="8" t="inlineStr">
+        <is>
+          <t>garden_view</t>
+        </is>
+      </c>
+      <c r="AE16" s="8" t="inlineStr">
+        <is>
+          <t>renovated_modern</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>550000</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>12791</v>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>1005 Lausanne,</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>1942</v>
+      </c>
+      <c r="K17" s="8" t="inlineStr"/>
+      <c r="L17" s="8" t="inlineStr"/>
+      <c r="M17" s="8" t="inlineStr"/>
+      <c r="N17" s="8" t="inlineStr"/>
+      <c r="O17" s="8" t="inlineStr"/>
+      <c r="P17" s="8" t="inlineStr"/>
+      <c r="Q17" s="8" t="inlineStr"/>
+      <c r="R17" s="8" t="inlineStr"/>
+      <c r="S17" s="8" t="inlineStr"/>
+      <c r="T17" s="8" t="inlineStr"/>
+      <c r="U17" s="8" t="inlineStr"/>
+      <c r="V17" s="8" t="inlineStr"/>
+      <c r="W17" s="8" t="inlineStr"/>
+      <c r="X17" s="8" t="inlineStr"/>
+      <c r="Y17" s="8" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/Medias/regie-duboux-riviera-2599/1479348/images/gridbig/30813804.jpg; https://www.immobilier.ch/Medias/regie-duboux-riviera-2599/1479348/images/full/30813804.jpg; https://www.immobilier.ch/Medias/regie-duboux-riviera-2599/1479348/images/full/30813798.jpg; https://www.immobilier.ch/Medias/regie-duboux-riviera-2599/1479348/images/full/30813807.jpg; https://www.immobilier.ch/Medias/regie-duboux-riviera-2599/1479348/images/full/30813814.jpg</t>
+        </is>
+      </c>
+      <c r="Z17" s="8" t="inlineStr">
+        <is>
+          <t>immobilier.ch</t>
+        </is>
+      </c>
+      <c r="AA17" s="8" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/regie-duboux-riviera-2599/25-room-apartment-lausanne-1479348</t>
+        </is>
+      </c>
+      <c r="AB17" s="8" t="inlineStr"/>
+      <c r="AC17" s="8" t="inlineStr">
+        <is>
           <t>upper_floor</t>
         </is>
       </c>
-      <c r="AC14" s="8" t="inlineStr">
+      <c r="AD17" s="8" t="inlineStr">
         <is>
           <t>open_view</t>
         </is>
       </c>
-      <c r="AD14" s="2" t="inlineStr">
-        <is>
-          <t>renovated_modern</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>Lausanne</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr"/>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="AE17" s="8" t="inlineStr">
+        <is>
+          <t>well_lit</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Morges</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>1110</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="F15" s="11" t="n">
-        <v>48</v>
-      </c>
-      <c r="G15" s="12" t="n">
-        <v>735000</v>
-      </c>
-      <c r="H15" s="12" t="n">
-        <v>15312</v>
-      </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>Lausanne</t>
-        </is>
-      </c>
-      <c r="J15" s="11" t="n">
-        <v>2026</v>
-      </c>
-      <c r="K15" s="11" t="inlineStr"/>
-      <c r="L15" s="11" t="inlineStr"/>
-      <c r="M15" s="11" t="inlineStr"/>
-      <c r="N15" s="11" t="inlineStr"/>
-      <c r="O15" s="11" t="inlineStr"/>
-      <c r="P15" s="11" t="inlineStr"/>
-      <c r="Q15" s="11" t="inlineStr"/>
-      <c r="R15" s="11" t="inlineStr"/>
-      <c r="S15" s="11" t="inlineStr"/>
-      <c r="T15" s="11" t="inlineStr"/>
-      <c r="U15" s="11" t="inlineStr"/>
-      <c r="V15" s="11" t="inlineStr"/>
-      <c r="W15" s="11" t="inlineStr"/>
-      <c r="X15" s="11" t="inlineStr"/>
-      <c r="Y15" s="11" t="inlineStr">
-        <is>
-          <t>https://www.immobilier.ch/Medias/properti-ag-2229/1578009/images/full/31816432.png; https://www.immobilier.ch/Medias/properti-ag-2229/1578009/images/full/31816434.png; https://www.immobilier.ch/Medias/properti-ag-2229/1578009/images/full/31816427.png; https://www.immobilier.ch/Medias/properti-ag-2229/1578009/images/full/31816426.jpeg; https://www.immobilier.ch/Medias/properti-ag-2229/1578009/images/full/31816431.jpg</t>
-        </is>
-      </c>
-      <c r="Z15" s="11" t="inlineStr">
+      <c r="F18" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>690000</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>13800</v>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>1110 Morges,</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="n">
+        <v>2027</v>
+      </c>
+      <c r="K18" s="8" t="inlineStr"/>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="inlineStr"/>
+      <c r="N18" s="8" t="inlineStr"/>
+      <c r="O18" s="8" t="inlineStr"/>
+      <c r="P18" s="8" t="inlineStr"/>
+      <c r="Q18" s="8" t="inlineStr"/>
+      <c r="R18" s="8" t="inlineStr"/>
+      <c r="S18" s="8" t="inlineStr"/>
+      <c r="T18" s="8" t="inlineStr"/>
+      <c r="U18" s="8" t="inlineStr"/>
+      <c r="V18" s="8" t="inlineStr"/>
+      <c r="W18" s="8" t="inlineStr"/>
+      <c r="X18" s="8" t="inlineStr"/>
+      <c r="Y18" s="8" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/Medias/immocloud-sarl-2545/1564549/images/full/31692610.png; https://www.immobilier.ch/Medias/immocloud-sarl-2545/1564549/images/full/31718844.jpg; https://www.immobilier.ch/Medias/immocloud-sarl-2545/1564549/images/full/31718848.jpg; https://www.immobilier.ch/Medias/immocloud-sarl-2545/1564549/images/full/31718849.jpg; https://www.immobilier.ch/Medias/immocloud-sarl-2545/1564549/images/full/31718842.jpg</t>
+        </is>
+      </c>
+      <c r="Z18" s="8" t="inlineStr">
         <is>
           <t>immobilier.ch</t>
         </is>
       </c>
-      <c r="AA15" s="11" t="inlineStr">
-        <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/properti-ag-2229/contemporary-address-in-the-heart-of-lausanne-1578009</t>
-        </is>
-      </c>
-      <c r="AB15" s="11" t="inlineStr"/>
-      <c r="AC15" s="11" t="inlineStr"/>
-      <c r="AD15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>Lausanne</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr"/>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>Apartment</t>
-        </is>
-      </c>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="F16" s="11" t="n">
-        <v>48</v>
-      </c>
-      <c r="G16" s="12" t="n">
-        <v>740000</v>
-      </c>
-      <c r="H16" s="12" t="n">
-        <v>15417</v>
-      </c>
-      <c r="I16" s="11" t="inlineStr">
-        <is>
-          <t>Lausanne</t>
-        </is>
-      </c>
-      <c r="J16" s="11" t="n">
-        <v>2026</v>
-      </c>
-      <c r="K16" s="11" t="inlineStr"/>
-      <c r="L16" s="11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M16" s="11" t="inlineStr"/>
-      <c r="N16" s="11" t="inlineStr"/>
-      <c r="O16" s="11" t="inlineStr"/>
-      <c r="P16" s="11" t="inlineStr"/>
-      <c r="Q16" s="11" t="inlineStr"/>
-      <c r="R16" s="11" t="inlineStr"/>
-      <c r="S16" s="11" t="inlineStr"/>
-      <c r="T16" s="11" t="inlineStr"/>
-      <c r="U16" s="11" t="inlineStr"/>
-      <c r="V16" s="11" t="inlineStr"/>
-      <c r="W16" s="11" t="inlineStr"/>
-      <c r="X16" s="11" t="inlineStr"/>
-      <c r="Y16" s="11" t="inlineStr">
-        <is>
-          <t>https://www.immobilier.ch/Medias/properti-ag-2229/1578011/images/full/31816454.jpeg; https://www.immobilier.ch/Medias/properti-ag-2229/1578011/images/full/31816453.jpeg; https://www.immobilier.ch/Medias/properti-ag-2229/1578011/images/gridbig/31816451.png; https://www.immobilier.ch/Medias/properti-ag-2229/1578011/images/full/31816455.jpg; https://www.immobilier.ch/Medias/properti-ag-2229/1578011/images/full/31816456.png</t>
-        </is>
-      </c>
-      <c r="Z16" s="11" t="inlineStr">
-        <is>
-          <t>immobilier.ch</t>
-        </is>
-      </c>
-      <c r="AA16" s="11" t="inlineStr">
-        <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/properti-ag-2229/contemporary-address-in-the-heart-of-lausanne-1578011</t>
-        </is>
-      </c>
-      <c r="AB16" s="11" t="inlineStr"/>
-      <c r="AC16" s="11" t="inlineStr"/>
-      <c r="AD16" s="2" t="inlineStr">
+      <c r="AA18" s="8" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/morges/immocloud-sarl-2545/promotion-residence-cedre-the-construction-site-is-open-1564549</t>
+        </is>
+      </c>
+      <c r="AB18" s="8" t="inlineStr"/>
+      <c r="AC18" s="8" t="inlineStr"/>
+      <c r="AD18" s="8" t="inlineStr"/>
+      <c r="AE18" s="8" t="inlineStr">
         <is>
           <t>well_lit</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Lausanne</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr"/>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>Apartment</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="F17" s="11" t="n">
-        <v>36</v>
-      </c>
-      <c r="G17" s="12" t="n">
-        <v>585000</v>
-      </c>
-      <c r="H17" s="12" t="n">
-        <v>16250</v>
-      </c>
-      <c r="I17" s="11" t="inlineStr">
-        <is>
-          <t>Lausanne</t>
-        </is>
-      </c>
-      <c r="J17" s="11" t="n">
-        <v>2026</v>
-      </c>
-      <c r="K17" s="11" t="inlineStr"/>
-      <c r="L17" s="11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M17" s="11" t="inlineStr"/>
-      <c r="N17" s="11" t="inlineStr"/>
-      <c r="O17" s="11" t="inlineStr"/>
-      <c r="P17" s="11" t="inlineStr"/>
-      <c r="Q17" s="11" t="inlineStr"/>
-      <c r="R17" s="11" t="inlineStr"/>
-      <c r="S17" s="11" t="inlineStr"/>
-      <c r="T17" s="11" t="inlineStr"/>
-      <c r="U17" s="11" t="inlineStr"/>
-      <c r="V17" s="11" t="inlineStr"/>
-      <c r="W17" s="11" t="inlineStr"/>
-      <c r="X17" s="11" t="inlineStr"/>
-      <c r="Y17" s="11" t="inlineStr">
-        <is>
-          <t>https://www.immobilier.ch/Medias/properti-ag-2229/1578014/images/full/31816484.jpeg; https://www.immobilier.ch/Medias/properti-ag-2229/1578014/images/full/31816485.jpeg; https://www.immobilier.ch/Medias/properti-ag-2229/1578014/images/full/31816489.jpg; https://www.immobilier.ch/Medias/properti-ag-2229/1578014/images/full/31816493.png; https://www.immobilier.ch/Medias/properti-ag-2229/1578014/images/gridbig/31816482.png</t>
-        </is>
-      </c>
-      <c r="Z17" s="11" t="inlineStr">
-        <is>
-          <t>immobilier.ch</t>
-        </is>
-      </c>
-      <c r="AA17" s="11" t="inlineStr">
-        <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/properti-ag-2229/contemporary-address-in-the-heart-of-lausanne-1578014</t>
-        </is>
-      </c>
-      <c r="AB17" s="11" t="inlineStr"/>
-      <c r="AC17" s="11" t="inlineStr"/>
-      <c r="AD17" s="2" t="inlineStr">
-        <is>
-          <t>well_lit</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>Lausanne</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr"/>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>Apartment</t>
-        </is>
-      </c>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="F18" s="11" t="n">
-        <v>29</v>
-      </c>
-      <c r="G18" s="12" t="n">
-        <v>475000</v>
-      </c>
-      <c r="H18" s="12" t="n">
-        <v>16379</v>
-      </c>
-      <c r="I18" s="11" t="inlineStr">
-        <is>
-          <t>Lausanne</t>
-        </is>
-      </c>
-      <c r="J18" s="11" t="n">
-        <v>2026</v>
-      </c>
-      <c r="K18" s="11" t="inlineStr"/>
-      <c r="L18" s="11" t="inlineStr"/>
-      <c r="M18" s="11" t="inlineStr"/>
-      <c r="N18" s="11" t="inlineStr"/>
-      <c r="O18" s="11" t="inlineStr"/>
-      <c r="P18" s="11" t="inlineStr"/>
-      <c r="Q18" s="11" t="inlineStr"/>
-      <c r="R18" s="11" t="inlineStr"/>
-      <c r="S18" s="11" t="inlineStr"/>
-      <c r="T18" s="11" t="inlineStr"/>
-      <c r="U18" s="11" t="inlineStr"/>
-      <c r="V18" s="11" t="inlineStr"/>
-      <c r="W18" s="11" t="inlineStr"/>
-      <c r="X18" s="11" t="inlineStr"/>
-      <c r="Y18" s="11" t="inlineStr">
-        <is>
-          <t>https://www.immobilier.ch/Medias/properti-ag-2229/1578008/images/full/31816414.jpeg; https://www.immobilier.ch/Medias/properti-ag-2229/1578008/images/full/31816421.jpg; https://www.immobilier.ch/Medias/properti-ag-2229/1578008/images/full/31816413.jpeg; https://www.immobilier.ch/Medias/properti-ag-2229/1578008/images/full/31816418.png; https://www.immobilier.ch/Medias/properti-ag-2229/1578008/images/full/31816425.png</t>
-        </is>
-      </c>
-      <c r="Z18" s="11" t="inlineStr">
-        <is>
-          <t>immobilier.ch</t>
-        </is>
-      </c>
-      <c r="AA18" s="11" t="inlineStr">
-        <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/properti-ag-2229/contemporary-address-in-the-heart-of-lausanne-1578008</t>
-        </is>
-      </c>
-      <c r="AB18" s="11" t="inlineStr"/>
-      <c r="AC18" s="11" t="inlineStr"/>
-      <c r="AD18" s="2" t="inlineStr">
-        <is>
-          <t>renovated_modern</t>
         </is>
       </c>
     </row>
@@ -3862,10 +4385,14 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Rolle</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr"/>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
           <t>Apartment</t>
@@ -3877,21 +4404,21 @@
         </is>
       </c>
       <c r="F19" s="11" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>780000</v>
+        <v>735000</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>17727</v>
+        <v>15312</v>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>Rolle</t>
+          <t>1010 Lausanne,</t>
         </is>
       </c>
       <c r="J19" s="11" t="n">
-        <v>2019</v>
+        <v>2028</v>
       </c>
       <c r="K19" s="11" t="inlineStr"/>
       <c r="L19" s="11" t="inlineStr"/>
@@ -3909,7 +4436,7 @@
       <c r="X19" s="11" t="inlineStr"/>
       <c r="Y19" s="11" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/cogestim-rolle-361/1559393/images/full/31642872.jpg; https://www.immobilier.ch/Medias/cogestim-rolle-361/1559393/images/full/31642858.jpg; https://www.immobilier.ch/Medias/cogestim-rolle-361/1559393/images/full/31642870.jpg; https://www.immobilier.ch/Medias/cogestim-rolle-361/1559393/images/full/31642861.jpg; https://www.immobilier.ch/Medias/cogestim-rolle-361/1559393/images/full/31642865.jpg</t>
+          <t>https://www.immobilier.ch/Medias/cardis-lausanne-429/1594481/images/full/31969367.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1594481/images/full/31969362.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1594481/images/full/31969366.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1594481/images/full/31969365.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1594481/images/full/31969358.png</t>
         </is>
       </c>
       <c r="Z19" s="11" t="inlineStr">
@@ -3919,24 +4446,13 @@
       </c>
       <c r="AA19" s="11" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/rolle/cogestim-rolle-361/charming-25-room-apartment-1559393</t>
-        </is>
-      </c>
-      <c r="AB19" s="11" t="inlineStr">
-        <is>
-          <t>middle_floor</t>
-        </is>
-      </c>
-      <c r="AC19" s="11" t="inlineStr">
-        <is>
-          <t>garden_view</t>
-        </is>
-      </c>
-      <c r="AD19" s="2" t="inlineStr">
-        <is>
-          <t>well_lit</t>
-        </is>
-      </c>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/switzerland-sothebys-lausanne-429/contemporary-25-room-apartment-with-balcony-lot-02-1594481</t>
+        </is>
+      </c>
+      <c r="AB19" s="11" t="inlineStr"/>
+      <c r="AC19" s="11" t="inlineStr"/>
+      <c r="AD19" s="11" t="inlineStr"/>
+      <c r="AE19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="10" t="n">
@@ -3947,32 +4463,38 @@
           <t>Lausanne</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr"/>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Terrace flat</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="F20" s="11" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>490000</v>
+        <v>735000</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>18846</v>
+        <v>15312</v>
       </c>
       <c r="I20" s="11" t="inlineStr">
         <is>
-          <t>Lausanne</t>
-        </is>
-      </c>
-      <c r="J20" s="11" t="inlineStr"/>
+          <t>1010 Lausanne,</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="n">
+        <v>2026</v>
+      </c>
       <c r="K20" s="11" t="inlineStr"/>
       <c r="L20" s="11" t="inlineStr"/>
       <c r="M20" s="11" t="inlineStr"/>
@@ -3981,11 +4503,7 @@
       <c r="P20" s="11" t="inlineStr"/>
       <c r="Q20" s="11" t="inlineStr"/>
       <c r="R20" s="11" t="inlineStr"/>
-      <c r="S20" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="S20" s="11" t="inlineStr"/>
       <c r="T20" s="11" t="inlineStr"/>
       <c r="U20" s="11" t="inlineStr"/>
       <c r="V20" s="11" t="inlineStr"/>
@@ -3993,7 +4511,7 @@
       <c r="X20" s="11" t="inlineStr"/>
       <c r="Y20" s="11" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/immo-v-3083/1574816/images/full/31787034.jpeg; https://www.immobilier.ch/Medias/immo-v-3083/1574816/images/full/31787030.jpeg; https://www.immobilier.ch/Medias/immo-v-3083/1574816/images/full/31787037.jpeg; https://www.immobilier.ch/Medias/immo-v-3083/1574816/images/full/31787040.jpeg; https://www.immobilier.ch/Medias/immo-v-3083/1574816/images/gridbig/31787042.png</t>
+          <t>https://www.immobilier.ch/Medias/properti-ag-2229/1592615/images/full/31952904.png; https://www.immobilier.ch/Medias/properti-ag-2229/1592615/images/full/31952895.jpeg; https://www.immobilier.ch/Medias/properti-ag-2229/1592615/images/full/31952907.png; https://www.immobilier.ch/Medias/properti-ag-2229/1592615/images/full/31952914.png; https://www.immobilier.ch/Medias/properti-ag-2229/1592615/images/gridbig/31952894.png</t>
         </is>
       </c>
       <c r="Z20" s="11" t="inlineStr">
@@ -4003,12 +4521,13 @@
       </c>
       <c r="AA20" s="11" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/immo-v-3083/renovated-and-furnished-with-terrace-ideal-location-1574816</t>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/properti-ag-2229/contemporary-address-in-the-heart-of-lausanne-1592615</t>
         </is>
       </c>
       <c r="AB20" s="11" t="inlineStr"/>
       <c r="AC20" s="11" t="inlineStr"/>
-      <c r="AD20" s="2" t="inlineStr">
+      <c r="AD20" s="11" t="inlineStr"/>
+      <c r="AE20" s="11" t="inlineStr">
         <is>
           <t>well_lit</t>
         </is>
@@ -4023,51 +4542,47 @@
           <t>Lausanne</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr"/>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Studio</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr"/>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
       <c r="F21" s="11" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>490000</v>
+        <v>740000</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>18846</v>
+        <v>15417</v>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>Lausanne</t>
+          <t>1010 Lausanne,</t>
         </is>
       </c>
       <c r="J21" s="11" t="n">
-        <v>1969</v>
+        <v>2028</v>
       </c>
       <c r="K21" s="11" t="inlineStr"/>
-      <c r="L21" s="11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="L21" s="11" t="inlineStr"/>
       <c r="M21" s="11" t="inlineStr"/>
       <c r="N21" s="11" t="inlineStr"/>
       <c r="O21" s="11" t="inlineStr"/>
       <c r="P21" s="11" t="inlineStr"/>
       <c r="Q21" s="11" t="inlineStr"/>
-      <c r="R21" s="11" t="inlineStr">
-        <is>
-          <t>Yes (from images)</t>
-        </is>
-      </c>
-      <c r="S21" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="R21" s="11" t="inlineStr"/>
+      <c r="S21" s="11" t="inlineStr"/>
       <c r="T21" s="11" t="inlineStr"/>
       <c r="U21" s="11" t="inlineStr"/>
       <c r="V21" s="11" t="inlineStr"/>
@@ -4075,7 +4590,7 @@
       <c r="X21" s="11" t="inlineStr"/>
       <c r="Y21" s="11" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/Medias/brymmo-2481/1545951/images/gridbig/31522051.jpg; https://www.immobilier.ch/Medias/brymmo-2481/1545951/images/full/31522052.jpg; https://www.immobilier.ch/Medias/brymmo-2481/1545951/images/full/31522056.jpg; https://www.immobilier.ch/Medias/brymmo-2481/1545951/images/full/31522054.jpg; https://www.immobilier.ch/Medias/brymmo-2481/1545951/images/full/31522055.jpg</t>
+          <t>https://www.immobilier.ch/Medias/cardis-lausanne-429/1594479/images/full/31969322.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1594479/images/full/31969331.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1594479/images/gridbig/31969331.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1594479/images/full/31969344.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1594479/images/full/31969340.png</t>
         </is>
       </c>
       <c r="Z21" s="11" t="inlineStr">
@@ -4085,18 +4600,1516 @@
       </c>
       <c r="AA21" s="11" t="inlineStr">
         <is>
-          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/brymmo-2481/jewel-in-the-heart-of-lausanne-1545951</t>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/switzerland-sothebys-lausanne-429/elegant-25-room-apartment-with-balcony-unit-05-1594479</t>
         </is>
       </c>
       <c r="AB21" s="11" t="inlineStr"/>
-      <c r="AC21" s="11" t="inlineStr">
-        <is>
-          <t>garden_view</t>
-        </is>
-      </c>
-      <c r="AD21" s="2" t="inlineStr">
+      <c r="AC21" s="11" t="inlineStr"/>
+      <c r="AD21" s="11" t="inlineStr"/>
+      <c r="AE21" s="11" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>48</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>750000</v>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>15625</v>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>1010 Lausanne,</t>
+        </is>
+      </c>
+      <c r="J22" s="11" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K22" s="11" t="inlineStr"/>
+      <c r="L22" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M22" s="11" t="inlineStr"/>
+      <c r="N22" s="11" t="inlineStr"/>
+      <c r="O22" s="11" t="inlineStr"/>
+      <c r="P22" s="11" t="inlineStr"/>
+      <c r="Q22" s="11" t="inlineStr"/>
+      <c r="R22" s="11" t="inlineStr"/>
+      <c r="S22" s="11" t="inlineStr"/>
+      <c r="T22" s="11" t="inlineStr"/>
+      <c r="U22" s="11" t="inlineStr"/>
+      <c r="V22" s="11" t="inlineStr"/>
+      <c r="W22" s="11" t="inlineStr"/>
+      <c r="X22" s="11" t="inlineStr"/>
+      <c r="Y22" s="11" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/Medias/properti-ag-2229/1592619/images/full/31952955.png; https://www.immobilier.ch/Medias/properti-ag-2229/1592619/images/full/31952947.jpeg; https://www.immobilier.ch/Medias/properti-ag-2229/1592619/images/full/31952953.jpg; https://www.immobilier.ch/Medias/properti-ag-2229/1592619/images/full/31952954.jpeg; https://www.immobilier.ch/Medias/properti-ag-2229/1592619/images/full/31952956.png</t>
+        </is>
+      </c>
+      <c r="Z22" s="11" t="inlineStr">
+        <is>
+          <t>immobilier.ch</t>
+        </is>
+      </c>
+      <c r="AA22" s="11" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/properti-ag-2229/contemporary-address-in-the-heart-of-lausanne-1592619</t>
+        </is>
+      </c>
+      <c r="AB22" s="11" t="inlineStr"/>
+      <c r="AC22" s="11" t="inlineStr"/>
+      <c r="AD22" s="11" t="inlineStr"/>
+      <c r="AE22" s="11" t="inlineStr">
         <is>
           <t>well_lit</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>480000</v>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>16552</v>
+      </c>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>1010 Lausanne,</t>
+        </is>
+      </c>
+      <c r="J23" s="11" t="n">
+        <v>2028</v>
+      </c>
+      <c r="K23" s="11" t="inlineStr"/>
+      <c r="L23" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M23" s="11" t="inlineStr"/>
+      <c r="N23" s="11" t="inlineStr"/>
+      <c r="O23" s="11" t="inlineStr"/>
+      <c r="P23" s="11" t="inlineStr"/>
+      <c r="Q23" s="11" t="inlineStr"/>
+      <c r="R23" s="11" t="inlineStr"/>
+      <c r="S23" s="11" t="inlineStr"/>
+      <c r="T23" s="11" t="inlineStr"/>
+      <c r="U23" s="11" t="inlineStr"/>
+      <c r="V23" s="11" t="inlineStr"/>
+      <c r="W23" s="11" t="inlineStr"/>
+      <c r="X23" s="11" t="inlineStr"/>
+      <c r="Y23" s="11" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/Medias/cardis-lausanne-429/1594482/images/full/31969369.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1594482/images/gridbig/31969369.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1594482/images/full/31969383.png; https://www.immobilier.ch/Medias/cardis-lausanne-429/1594482/images/full/31969374.jpg; https://www.immobilier.ch/Medias/cardis-lausanne-429/1594482/images/full/31969373.png</t>
+        </is>
+      </c>
+      <c r="Z23" s="11" t="inlineStr">
+        <is>
+          <t>immobilier.ch</t>
+        </is>
+      </c>
+      <c r="AA23" s="11" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/switzerland-sothebys-lausanne-429/contemporary-bright-studio-apartment-in-lausanne-lot-07-1594482</t>
+        </is>
+      </c>
+      <c r="AB23" s="11" t="inlineStr"/>
+      <c r="AC23" s="11" t="inlineStr"/>
+      <c r="AD23" s="11" t="inlineStr"/>
+      <c r="AE23" s="11" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Terrace flat</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>490000</v>
+      </c>
+      <c r="H24" s="12" t="n">
+        <v>18846</v>
+      </c>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>1004 Lausanne,</t>
+        </is>
+      </c>
+      <c r="J24" s="11" t="inlineStr"/>
+      <c r="K24" s="11" t="inlineStr"/>
+      <c r="L24" s="11" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M24" s="11" t="inlineStr"/>
+      <c r="N24" s="11" t="inlineStr"/>
+      <c r="O24" s="11" t="inlineStr"/>
+      <c r="P24" s="11" t="inlineStr"/>
+      <c r="Q24" s="11" t="inlineStr"/>
+      <c r="R24" s="11" t="inlineStr"/>
+      <c r="S24" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T24" s="11" t="inlineStr"/>
+      <c r="U24" s="11" t="inlineStr"/>
+      <c r="V24" s="11" t="inlineStr"/>
+      <c r="W24" s="11" t="inlineStr"/>
+      <c r="X24" s="11" t="inlineStr"/>
+      <c r="Y24" s="11" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/Medias/immo-v-3083/1588642/images/full/31916408.jpeg; https://www.immobilier.ch/Medias/immo-v-3083/1588642/images/full/31916411.jpeg; https://www.immobilier.ch/Medias/immo-v-3083/1588642/images/full/31916407.jpeg; https://www.immobilier.ch/Medias/immo-v-3083/1588642/images/full/31916396.jpeg; https://www.immobilier.ch/Medias/immo-v-3083/1588642/images/full/31916415.png</t>
+        </is>
+      </c>
+      <c r="Z24" s="11" t="inlineStr">
+        <is>
+          <t>immobilier.ch</t>
+        </is>
+      </c>
+      <c r="AA24" s="11" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/immo-v-3083/renovated-and-furnished-with-terrace-ideal-location-1588642</t>
+        </is>
+      </c>
+      <c r="AB24" s="11" t="inlineStr"/>
+      <c r="AC24" s="11" t="inlineStr"/>
+      <c r="AD24" s="11" t="inlineStr"/>
+      <c r="AE24" s="11" t="inlineStr">
+        <is>
+          <t>well_lit</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="65" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>NPA</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>Rooms</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>Size (m2)</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>Price (CHF)</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Price/m2 (CHF)</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>Why this is a good investment</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>Morges</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>1110</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E2" s="16" t="n">
+        <v>85</v>
+      </c>
+      <c r="F2" s="16" t="n">
+        <v>760000</v>
+      </c>
+      <c r="G2" s="16" t="n">
+        <v>8941</v>
+      </c>
+      <c r="H2" s="17" t="n">
+        <v>74</v>
+      </c>
+      <c r="I2" s="18" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+      <c r="J2" s="19" t="inlineStr"/>
+      <c r="K2" s="19" t="inlineStr">
+        <is>
+          <t>Great value: CHF 8941/m2; Good size (85m2); Renovated/modern - no work needed; Amenities: Lake/panoramic view; Open view from images; 4.0 rooms - optimal rental size</t>
+        </is>
+      </c>
+      <c r="L2" s="15" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/morges/vpi-courtage-467/for-sale-apartment-1110-morges-6257755-1587969</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>Morges</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>1110</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="n">
+        <v>109</v>
+      </c>
+      <c r="F3" s="16" t="n">
+        <v>730000</v>
+      </c>
+      <c r="G3" s="16" t="n">
+        <v>6697</v>
+      </c>
+      <c r="H3" s="17" t="n">
+        <v>72</v>
+      </c>
+      <c r="I3" s="18" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+      <c r="J3" s="19" t="inlineStr"/>
+      <c r="K3" s="19" t="inlineStr">
+        <is>
+          <t>Excellent value: CHF 6697/m2 (way below average); Large apartment (109m2) - high rental appeal; Renovated/modern - no work needed; Amenities: Renovated; 3.5 rooms - optimal rental size</t>
+        </is>
+      </c>
+      <c r="L3" s="15" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/morges/sev-immobilier-3069/for-sale-condominium-apartment-1110-morges-20261009-1592927</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>129</v>
+      </c>
+      <c r="F4" s="16" t="n">
+        <v>770000</v>
+      </c>
+      <c r="G4" s="16" t="n">
+        <v>5969</v>
+      </c>
+      <c r="H4" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="I4" s="18" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr"/>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>Excellent value: CHF 5969/m2 (way below average); Large apartment (129m2) - high rental appeal; Bright and well-lit; Amenities: Lake/panoramic view; Garden view from images; 5.5 rooms - family rental appeal</t>
+        </is>
+      </c>
+      <c r="L4" s="15" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/proximmo-agence-immobiliere-sarl-622/votre-logement-familial-20-min-lausanne-1485790</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>Gland</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>1196</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="n">
+        <v>82</v>
+      </c>
+      <c r="F5" s="22" t="n">
+        <v>780000</v>
+      </c>
+      <c r="G5" s="22" t="n">
+        <v>9512</v>
+      </c>
+      <c r="H5" s="23" t="n">
+        <v>69</v>
+      </c>
+      <c r="I5" s="24" t="inlineStr">
+        <is>
+          <t>Very Good</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="inlineStr"/>
+      <c r="K5" s="25" t="inlineStr">
+        <is>
+          <t>Great value: CHF 9512/m2; Good size (82m2); Bright and well-lit; Amenities: Lake/panoramic view; Open view from images; 3.5 rooms - optimal rental size</t>
+        </is>
+      </c>
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/gland/omnia-immobilier-rolle-445/beautiful-35-room-apartment-in-gland-1460475</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>Gland</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>1196</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="n">
+        <v>82</v>
+      </c>
+      <c r="F6" s="22" t="n">
+        <v>780000</v>
+      </c>
+      <c r="G6" s="22" t="n">
+        <v>9512</v>
+      </c>
+      <c r="H6" s="23" t="n">
+        <v>69</v>
+      </c>
+      <c r="I6" s="24" t="inlineStr">
+        <is>
+          <t>Very Good</t>
+        </is>
+      </c>
+      <c r="J6" s="25" t="inlineStr"/>
+      <c r="K6" s="25" t="inlineStr">
+        <is>
+          <t>Great value: CHF 9512/m2; Good size (82m2); Bright and well-lit; Amenities: Lake/panoramic view; Open view from images; 3.5 rooms - optimal rental size</t>
+        </is>
+      </c>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/gland/dezage-sarl-2077/charming-apartment-close-to-all-amenities-1581074</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>Gland</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>1196</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="n">
+        <v>73</v>
+      </c>
+      <c r="F7" s="22" t="n">
+        <v>795000</v>
+      </c>
+      <c r="G7" s="22" t="n">
+        <v>10890</v>
+      </c>
+      <c r="H7" s="23" t="n">
+        <v>55</v>
+      </c>
+      <c r="I7" s="24" t="inlineStr">
+        <is>
+          <t>Very Good</t>
+        </is>
+      </c>
+      <c r="J7" s="25" t="inlineStr"/>
+      <c r="K7" s="25" t="inlineStr">
+        <is>
+          <t>Good value: CHF 10890/m2; Medium size (73m2); Bright and well-lit; Amenities: Lake/panoramic view; Garden view from images; 3.5 rooms - optimal rental size</t>
+        </is>
+      </c>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/gland/burnier-cie-233/35-room-apartment-in-gland-1576776</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>43</v>
+      </c>
+      <c r="F8" s="26" t="n">
+        <v>550000</v>
+      </c>
+      <c r="G8" s="26" t="n">
+        <v>12791</v>
+      </c>
+      <c r="H8" s="27" t="n">
+        <v>48</v>
+      </c>
+      <c r="I8" s="28" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="J8" s="29" t="inlineStr"/>
+      <c r="K8" s="29" t="inlineStr">
+        <is>
+          <t>Fair value: CHF 12791/m2; Bright and well-lit; Open view from images; 2.5 rooms - optimal rental size</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/regie-duboux-riviera-2599/25-room-apartment-lausanne-1479348</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Nyon</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>1260</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>81</v>
+      </c>
+      <c r="F9" s="26" t="n">
+        <v>670000</v>
+      </c>
+      <c r="G9" s="26" t="n">
+        <v>8272</v>
+      </c>
+      <c r="H9" s="27" t="n">
+        <v>47</v>
+      </c>
+      <c r="I9" s="28" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="J9" s="29" t="inlineStr"/>
+      <c r="K9" s="29" t="inlineStr">
+        <is>
+          <t>Great value: CHF 8272/m2; Good size (81m2); 3.5 rooms - optimal rental size</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/nyon/cologny-properties-3110/luxury-apartment-1593459</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Gland</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>1196</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>80</v>
+      </c>
+      <c r="F10" s="26" t="n">
+        <v>720000</v>
+      </c>
+      <c r="G10" s="26" t="n">
+        <v>9000</v>
+      </c>
+      <c r="H10" s="27" t="n">
+        <v>47</v>
+      </c>
+      <c r="I10" s="28" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="J10" s="30" t="inlineStr">
+        <is>
+          <t>Rented - tenant in place</t>
+        </is>
+      </c>
+      <c r="K10" s="29" t="inlineStr">
+        <is>
+          <t>Great value: CHF 9000/m2; Good size (80m2); Bright and well-lit; Garden view from images; 3.5 rooms - optimal rental size; Note: Rented - tenant in place - income but not usable</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/gland/ikami-1611/magnificent-35-room-apartment-for-sale-gland-sold-with-tenant-078-403-10-20-1584268</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>81</v>
+      </c>
+      <c r="F11" s="26" t="n">
+        <v>670000</v>
+      </c>
+      <c r="G11" s="26" t="n">
+        <v>8272</v>
+      </c>
+      <c r="H11" s="27" t="n">
+        <v>47</v>
+      </c>
+      <c r="I11" s="28" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="J11" s="29" t="inlineStr"/>
+      <c r="K11" s="29" t="inlineStr">
+        <is>
+          <t>Great value: CHF 8272/m2; Good size (81m2); 3.5 rooms - optimal rental size</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/cologny-properties-3110/luxury-apartment-1593712</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>75</v>
+      </c>
+      <c r="F12" s="26" t="n">
+        <v>750000</v>
+      </c>
+      <c r="G12" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H12" s="27" t="n">
+        <v>45</v>
+      </c>
+      <c r="I12" s="28" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="J12" s="29" t="inlineStr"/>
+      <c r="K12" s="29" t="inlineStr">
+        <is>
+          <t>Good value: CHF 10000/m2; Good size (75m2); Needs work - renovation costs; 3.5 rooms - optimal rental size</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/rham-ventes-lausanne-1873/for-sale-condominium-apartment-1010-lausanne-ap0192-1455126</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>75</v>
+      </c>
+      <c r="F13" s="26" t="n">
+        <v>755000</v>
+      </c>
+      <c r="G13" s="26" t="n">
+        <v>10067</v>
+      </c>
+      <c r="H13" s="27" t="n">
+        <v>42</v>
+      </c>
+      <c r="I13" s="28" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="J13" s="29" t="inlineStr"/>
+      <c r="K13" s="29" t="inlineStr">
+        <is>
+          <t>Good value: CHF 10067/m2; Good size (75m2); 3.5 rooms - optimal rental size</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/switzerland-sothebys-lausanne-429/bright-apartment-with-wonderful-potential-1551036</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Morges</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>1110</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="F14" s="26" t="n">
+        <v>690000</v>
+      </c>
+      <c r="G14" s="26" t="n">
+        <v>13800</v>
+      </c>
+      <c r="H14" s="27" t="n">
+        <v>41</v>
+      </c>
+      <c r="I14" s="28" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="J14" s="29" t="inlineStr"/>
+      <c r="K14" s="29" t="inlineStr">
+        <is>
+          <t>Fair value: CHF 13800/m2; Medium size (50m2); Bright and well-lit; 2.5 rooms - optimal rental size</t>
+        </is>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/morges/immocloud-sarl-2545/promotion-residence-cedre-the-construction-site-is-open-1564549</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="E15" s="33" t="n">
+        <v>48</v>
+      </c>
+      <c r="F15" s="33" t="n">
+        <v>735000</v>
+      </c>
+      <c r="G15" s="33" t="n">
+        <v>15312</v>
+      </c>
+      <c r="H15" s="34" t="n">
+        <v>32</v>
+      </c>
+      <c r="I15" s="35" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="J15" s="36" t="inlineStr"/>
+      <c r="K15" s="36" t="inlineStr">
+        <is>
+          <t>Average value: CHF 15312/m2; Bright and well-lit; 2.5 rooms - optimal rental size</t>
+        </is>
+      </c>
+      <c r="L15" s="32" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/properti-ag-2229/contemporary-address-in-the-heart-of-lausanne-1592615</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="32" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="D16" s="32" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="E16" s="33" t="n">
+        <v>48</v>
+      </c>
+      <c r="F16" s="33" t="n">
+        <v>750000</v>
+      </c>
+      <c r="G16" s="33" t="n">
+        <v>15625</v>
+      </c>
+      <c r="H16" s="34" t="n">
+        <v>32</v>
+      </c>
+      <c r="I16" s="35" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="J16" s="36" t="inlineStr"/>
+      <c r="K16" s="36" t="inlineStr">
+        <is>
+          <t>Average value: CHF 15625/m2; Bright and well-lit; 2.5 rooms - optimal rental size</t>
+        </is>
+      </c>
+      <c r="L16" s="32" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/properti-ag-2229/contemporary-address-in-the-heart-of-lausanne-1592619</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="32" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="D17" s="32" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="E17" s="33" t="n">
+        <v>49</v>
+      </c>
+      <c r="F17" s="33" t="n">
+        <v>585000</v>
+      </c>
+      <c r="G17" s="33" t="n">
+        <v>11939</v>
+      </c>
+      <c r="H17" s="34" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="35" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="J17" s="37" t="inlineStr">
+        <is>
+          <t>Rented - tenant in place</t>
+        </is>
+      </c>
+      <c r="K17" s="36" t="inlineStr">
+        <is>
+          <t>Good value: CHF 11939/m2; Needs work - renovation costs; Amenities: Renovated; Garden view from images; 2.5 rooms - optimal rental size; Note: Rented - tenant in place - income but not usable</t>
+        </is>
+      </c>
+      <c r="L17" s="32" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/proximmo-agence-immobiliere-sarl-622/emplacement-rare-deux-pas-centre-ville-1581149</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="32" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="inlineStr">
+        <is>
+          <t>1012</t>
+        </is>
+      </c>
+      <c r="D18" s="32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E18" s="33" t="n">
+        <v>44</v>
+      </c>
+      <c r="F18" s="33" t="n">
+        <v>560000</v>
+      </c>
+      <c r="G18" s="33" t="n">
+        <v>12727</v>
+      </c>
+      <c r="H18" s="34" t="n">
+        <v>29</v>
+      </c>
+      <c r="I18" s="35" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="J18" s="37" t="inlineStr">
+        <is>
+          <t>Rented - tenant in place</t>
+        </is>
+      </c>
+      <c r="K18" s="36" t="inlineStr">
+        <is>
+          <t>Fair value: CHF 12727/m2; Renovated/modern - no work needed; Garden view from images; Note: Rented - tenant in place - income but not usable</t>
+        </is>
+      </c>
+      <c r="L18" s="32" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/golay-immobilier-260/rented-2-room-apartment-lausanne-bethusy-district-1593194</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="32" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="D19" s="32" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="E19" s="33" t="n">
+        <v>49</v>
+      </c>
+      <c r="F19" s="33" t="n">
+        <v>550000</v>
+      </c>
+      <c r="G19" s="33" t="n">
+        <v>11224</v>
+      </c>
+      <c r="H19" s="34" t="n">
+        <v>27</v>
+      </c>
+      <c r="I19" s="35" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="J19" s="37" t="inlineStr">
+        <is>
+          <t>Rented - tenant in place</t>
+        </is>
+      </c>
+      <c r="K19" s="36" t="inlineStr">
+        <is>
+          <t>Good value: CHF 11224/m2; Amenities: Renovated; Garden view from images; 2.5 rooms - optimal rental size; Note: Rented - tenant in place - income but not usable</t>
+        </is>
+      </c>
+      <c r="L19" s="32" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/proximmo-agence-immobiliere-sarl-622/emplacement-rare-deux-pas-centre-ville-1581148</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="38" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="39" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="C20" s="39" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="D20" s="39" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="E20" s="40" t="n">
+        <v>48</v>
+      </c>
+      <c r="F20" s="40" t="n">
+        <v>740000</v>
+      </c>
+      <c r="G20" s="40" t="n">
+        <v>15417</v>
+      </c>
+      <c r="H20" s="41" t="n">
+        <v>22</v>
+      </c>
+      <c r="I20" s="42" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="J20" s="43" t="inlineStr"/>
+      <c r="K20" s="43" t="inlineStr">
+        <is>
+          <t>Average value: CHF 15417/m2; 2.5 rooms - optimal rental size</t>
+        </is>
+      </c>
+      <c r="L20" s="39" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/switzerland-sothebys-lausanne-429/elegant-25-room-apartment-with-balcony-unit-05-1594479</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="38" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="39" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="C21" s="39" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="D21" s="39" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="E21" s="40" t="n">
+        <v>48</v>
+      </c>
+      <c r="F21" s="40" t="n">
+        <v>735000</v>
+      </c>
+      <c r="G21" s="40" t="n">
+        <v>15312</v>
+      </c>
+      <c r="H21" s="41" t="n">
+        <v>22</v>
+      </c>
+      <c r="I21" s="42" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="J21" s="43" t="inlineStr"/>
+      <c r="K21" s="43" t="inlineStr">
+        <is>
+          <t>Average value: CHF 15312/m2; 2.5 rooms - optimal rental size</t>
+        </is>
+      </c>
+      <c r="L21" s="39" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/switzerland-sothebys-lausanne-429/contemporary-25-room-apartment-with-balcony-lot-02-1594481</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="38" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="39" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="C22" s="39" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="D22" s="39" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="E22" s="40" t="n">
+        <v>26</v>
+      </c>
+      <c r="F22" s="40" t="n">
+        <v>490000</v>
+      </c>
+      <c r="G22" s="40" t="n">
+        <v>18846</v>
+      </c>
+      <c r="H22" s="41" t="n">
+        <v>20</v>
+      </c>
+      <c r="I22" s="42" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="J22" s="43" t="inlineStr"/>
+      <c r="K22" s="43" t="inlineStr">
+        <is>
+          <t>Expensive: CHF 18846/m2; Bright and well-lit; Amenities: Renovated</t>
+        </is>
+      </c>
+      <c r="L22" s="39" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/immo-v-3083/renovated-and-furnished-with-terrace-ideal-location-1588642</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="38" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="39" t="inlineStr">
+        <is>
+          <t>Gland</t>
+        </is>
+      </c>
+      <c r="C23" s="39" t="inlineStr">
+        <is>
+          <t>1196</t>
+        </is>
+      </c>
+      <c r="D23" s="39" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="E23" s="40" t="n">
+        <v>88</v>
+      </c>
+      <c r="F23" s="40" t="n">
+        <v>550000</v>
+      </c>
+      <c r="G23" s="40" t="n">
+        <v>6250</v>
+      </c>
+      <c r="H23" s="41" t="n">
+        <v>14</v>
+      </c>
+      <c r="I23" s="42" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="J23" s="44" t="inlineStr">
+        <is>
+          <t>Life annuity - occupied until 76yo dies</t>
+        </is>
+      </c>
+      <c r="K23" s="43" t="inlineStr">
+        <is>
+          <t>Excellent value: CHF 6250/m2 (way below average); Good size (88m2); Amenities: Renovated; 3.5 rooms - optimal rental size; WARNING: Life annuity - occupied until 76yo dies - property NOT usable now!</t>
+        </is>
+      </c>
+      <c r="L23" s="39" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/gland/immo-vie-agee-sarl-2312/through-apartment-with-balconies-in-life-annuity-in-gland-1591176</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="38" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="39" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="C24" s="39" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="D24" s="39" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="E24" s="40" t="n">
+        <v>29</v>
+      </c>
+      <c r="F24" s="40" t="n">
+        <v>480000</v>
+      </c>
+      <c r="G24" s="40" t="n">
+        <v>16552</v>
+      </c>
+      <c r="H24" s="41" t="n">
+        <v>8</v>
+      </c>
+      <c r="I24" s="42" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="J24" s="43" t="inlineStr"/>
+      <c r="K24" s="43" t="inlineStr">
+        <is>
+          <t>Expensive: CHF 16552/m2</t>
+        </is>
+      </c>
+      <c r="L24" s="39" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/switzerland-sothebys-lausanne-429/contemporary-bright-studio-apartment-in-lausanne-lot-07-1594482</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="38" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="39" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="C25" s="39" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="D25" s="39" t="inlineStr"/>
+      <c r="E25" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="40" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G25" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="41" t="n">
+        <v>8</v>
+      </c>
+      <c r="I25" s="42" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+      <c r="J25" s="43" t="inlineStr"/>
+      <c r="K25" s="43" t="inlineStr">
+        <is>
+          <t>Garden view from images</t>
+        </is>
+      </c>
+      <c r="L25" s="39" t="inlineStr">
+        <is>
+          <t>https://www.immobilier.ch/en/buy/apartment/vaud/lausanne/proximmo-agence-immobiliere-sarl-622/opportunities-for-private-investors-1484766</t>
         </is>
       </c>
     </row>
